--- a/research/traditional_assets/database/data/singapore/singapore_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_homebuilding.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08760092375001127</v>
+        <v>0.08748935217963626</v>
       </c>
       <c r="C2">
-        <v>140.8816670185013</v>
+        <v>139.8484029302645</v>
       </c>
       <c r="D2">
-        <v>140.7676670185013</v>
+        <v>141.1443979784742</v>
       </c>
       <c r="E2">
-        <v>-0.9995048209726342</v>
+        <v>0.4104902272370924</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.409995048209727</v>
       </c>
       <c r="G2">
         <v>0.114</v>
@@ -1433,28 +1433,28 @@
         <v>2.311</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07092275092494923</v>
       </c>
       <c r="N2">
-        <v>2.311</v>
+        <v>2.240077249075051</v>
       </c>
       <c r="O2">
-        <v>0.39287</v>
+        <v>0.3808131323427587</v>
       </c>
       <c r="P2">
-        <v>1.91813</v>
+        <v>1.859264116732292</v>
       </c>
       <c r="Q2">
-        <v>1.95313</v>
+        <v>1.894264116732292</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08760092375001127</v>
+        <v>0.08795137593902652</v>
       </c>
       <c r="T2">
-        <v>0.9653793013859414</v>
+        <v>0.9734728854278639</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>32.58474847437193</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08748935217963626</v>
+        <v>0.08737778060926123</v>
       </c>
       <c r="C3">
-        <v>139.8484029302645</v>
+        <v>138.8171607135272</v>
       </c>
       <c r="D3">
-        <v>141.1443979784742</v>
+        <v>141.5231508099466</v>
       </c>
       <c r="E3">
-        <v>0.4104902272370924</v>
+        <v>1.820485275446819</v>
       </c>
       <c r="F3">
-        <v>1.409995048209727</v>
+        <v>2.819990096419453</v>
       </c>
       <c r="G3">
         <v>0.114</v>
@@ -1515,28 +1515,28 @@
         <v>2.311</v>
       </c>
       <c r="M3">
-        <v>0.07092275092494923</v>
+        <v>0.1418455018498985</v>
       </c>
       <c r="N3">
-        <v>2.240077249075051</v>
+        <v>2.169154498150101</v>
       </c>
       <c r="O3">
-        <v>0.3808131323427587</v>
+        <v>0.3687562646855173</v>
       </c>
       <c r="P3">
-        <v>1.859264116732292</v>
+        <v>1.800398233464584</v>
       </c>
       <c r="Q3">
-        <v>1.894264116732292</v>
+        <v>1.835398233464584</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08795137593902652</v>
+        <v>0.08830898021353187</v>
       </c>
       <c r="T3">
-        <v>0.9734728854278639</v>
+        <v>0.9817316446543156</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>32.58474847437193</v>
+        <v>16.29237423718596</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08737778060926123</v>
+        <v>0.08730355903888622</v>
       </c>
       <c r="C4">
-        <v>138.8171607135272</v>
+        <v>137.6602540929314</v>
       </c>
       <c r="D4">
-        <v>141.5231508099466</v>
+        <v>141.7762392375606</v>
       </c>
       <c r="E4">
-        <v>1.820485275446819</v>
+        <v>3.230480323656545</v>
       </c>
       <c r="F4">
-        <v>2.819990096419453</v>
+        <v>4.229985144629179</v>
       </c>
       <c r="G4">
         <v>0.114</v>
@@ -1597,45 +1597,45 @@
         <v>2.311</v>
       </c>
       <c r="M4">
-        <v>0.1418455018498985</v>
+        <v>0.2191132304917915</v>
       </c>
       <c r="N4">
-        <v>2.169154498150101</v>
+        <v>2.091886769508208</v>
       </c>
       <c r="O4">
-        <v>0.3687562646855173</v>
+        <v>0.3556207508163954</v>
       </c>
       <c r="P4">
-        <v>1.800398233464584</v>
+        <v>1.736266018691813</v>
       </c>
       <c r="Q4">
-        <v>1.835398233464584</v>
+        <v>1.771266018691813</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08830898021353187</v>
+        <v>0.08867395777204765</v>
       </c>
       <c r="T4">
-        <v>0.9817316446543156</v>
+        <v>0.9901606875761578</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.17</v>
       </c>
       <c r="W4">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>16.29237423718596</v>
+        <v>10.54705822561717</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08730355903888622</v>
+        <v>0.0872608774685112</v>
       </c>
       <c r="C5">
-        <v>137.6602540929314</v>
+        <v>136.3962094659861</v>
       </c>
       <c r="D5">
-        <v>141.7762392375606</v>
+        <v>141.922189658825</v>
       </c>
       <c r="E5">
-        <v>3.230480323656545</v>
+        <v>4.640475371866272</v>
       </c>
       <c r="F5">
-        <v>4.229985144629179</v>
+        <v>5.639980192838906</v>
       </c>
       <c r="G5">
         <v>0.114</v>
@@ -1679,45 +1679,45 @@
         <v>2.311</v>
       </c>
       <c r="M5">
-        <v>0.2191132304917915</v>
+        <v>0.3017389403168815</v>
       </c>
       <c r="N5">
-        <v>2.091886769508208</v>
+        <v>2.009261059683118</v>
       </c>
       <c r="O5">
-        <v>0.3556207508163954</v>
+        <v>0.3415743801461302</v>
       </c>
       <c r="P5">
-        <v>1.736266018691813</v>
+        <v>1.667686679536988</v>
       </c>
       <c r="Q5">
-        <v>1.771266018691813</v>
+        <v>1.702686679536988</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08867395777204765</v>
+        <v>0.08904653902969917</v>
       </c>
       <c r="T5">
-        <v>0.9901606875761578</v>
+        <v>0.9987653355588719</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.17</v>
       </c>
       <c r="W5">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>10.54705822561717</v>
+        <v>7.65893854327527</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0872608774685112</v>
+        <v>0.08725056589813618</v>
       </c>
       <c r="C6">
-        <v>136.3962094659861</v>
+        <v>135.0215201033499</v>
       </c>
       <c r="D6">
-        <v>141.922189658825</v>
+        <v>141.9574953443985</v>
       </c>
       <c r="E6">
-        <v>4.640475371866272</v>
+        <v>6.050470420075999</v>
       </c>
       <c r="F6">
-        <v>5.639980192838906</v>
+        <v>7.049975241048632</v>
       </c>
       <c r="G6">
         <v>0.114</v>
@@ -1761,45 +1761,45 @@
         <v>2.311</v>
       </c>
       <c r="M6">
-        <v>0.3017389403168815</v>
+        <v>0.3898636308299894</v>
       </c>
       <c r="N6">
-        <v>2.009261059683118</v>
+        <v>1.921136369170011</v>
       </c>
       <c r="O6">
-        <v>0.3415743801461302</v>
+        <v>0.3265931827589018</v>
       </c>
       <c r="P6">
-        <v>1.667686679536988</v>
+        <v>1.594543186411109</v>
       </c>
       <c r="Q6">
-        <v>1.702686679536988</v>
+        <v>1.629543186411109</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08904653902969917</v>
+        <v>0.08942696410330124</v>
       </c>
       <c r="T6">
-        <v>0.9987653355588719</v>
+        <v>1.007551134025433</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0553</v>
       </c>
       <c r="V6">
         <v>0.17</v>
       </c>
       <c r="W6">
-        <v>0.044405</v>
+        <v>0.045899</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y6">
-        <v>7.65893854327527</v>
+        <v>5.927713736929142</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08725056589813618</v>
+        <v>0.08718049432776115</v>
       </c>
       <c r="C7">
-        <v>135.0215201033499</v>
+        <v>133.8519084721796</v>
       </c>
       <c r="D7">
-        <v>141.9574953443985</v>
+        <v>142.197878761438</v>
       </c>
       <c r="E7">
-        <v>6.050470420075999</v>
+        <v>7.460465468285726</v>
       </c>
       <c r="F7">
-        <v>7.049975241048632</v>
+        <v>8.45997028925836</v>
       </c>
       <c r="G7">
         <v>0.114</v>
@@ -1843,28 +1843,28 @@
         <v>2.311</v>
       </c>
       <c r="M7">
-        <v>0.3898636308299894</v>
+        <v>0.4678363569959873</v>
       </c>
       <c r="N7">
-        <v>1.921136369170011</v>
+        <v>1.843163643004013</v>
       </c>
       <c r="O7">
-        <v>0.3265931827589018</v>
+        <v>0.3133378193106822</v>
       </c>
       <c r="P7">
-        <v>1.594543186411109</v>
+        <v>1.52982582369333</v>
       </c>
       <c r="Q7">
-        <v>1.629543186411109</v>
+        <v>1.56482582369333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08942696410330124</v>
+        <v>0.08981548332740549</v>
       </c>
       <c r="T7">
-        <v>1.007551134025433</v>
+        <v>1.01652386437426</v>
       </c>
       <c r="U7">
         <v>0.0553</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>5.927713736929142</v>
+        <v>4.939761447440951</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08718049432776115</v>
+        <v>0.08725567275738615</v>
       </c>
       <c r="C8">
-        <v>133.8519084721796</v>
+        <v>132.1840424859235</v>
       </c>
       <c r="D8">
-        <v>142.197878761438</v>
+        <v>141.9400078233916</v>
       </c>
       <c r="E8">
-        <v>7.460465468285724</v>
+        <v>8.87046051649545</v>
       </c>
       <c r="F8">
-        <v>8.459970289258358</v>
+        <v>9.869965337468084</v>
       </c>
       <c r="G8">
         <v>0.114</v>
@@ -1925,45 +1925,45 @@
         <v>2.311</v>
       </c>
       <c r="M8">
-        <v>0.4678363569959872</v>
+        <v>0.5704839965056553</v>
       </c>
       <c r="N8">
-        <v>1.843163643004013</v>
+        <v>1.740516003494345</v>
       </c>
       <c r="O8">
-        <v>0.3133378193106822</v>
+        <v>0.2958877205940386</v>
       </c>
       <c r="P8">
-        <v>1.529825823693331</v>
+        <v>1.444628282900306</v>
       </c>
       <c r="Q8">
-        <v>1.564825823693331</v>
+        <v>1.479628282900306</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08981548332740549</v>
+        <v>0.09021235780364101</v>
       </c>
       <c r="T8">
-        <v>1.01652386437426</v>
+        <v>1.025689556666074</v>
       </c>
       <c r="U8">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V8">
         <v>0.17</v>
       </c>
       <c r="W8">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y8">
-        <v>4.939761447440953</v>
+        <v>4.050946238904864</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08725567275738613</v>
+        <v>0.08762467118701112</v>
       </c>
       <c r="C9">
-        <v>132.1840424859236</v>
+        <v>129.5217808089195</v>
       </c>
       <c r="D9">
-        <v>141.9400078233916</v>
+        <v>140.6877411945973</v>
       </c>
       <c r="E9">
-        <v>8.870460516495452</v>
+        <v>10.28045556470518</v>
       </c>
       <c r="F9">
-        <v>9.869965337468086</v>
+        <v>11.27996038567781</v>
       </c>
       <c r="G9">
         <v>0.114</v>
@@ -2007,45 +2007,45 @@
         <v>2.311</v>
       </c>
       <c r="M9">
-        <v>0.5704839965056554</v>
+        <v>0.7230454607219479</v>
       </c>
       <c r="N9">
-        <v>1.740516003494345</v>
+        <v>1.587954539278052</v>
       </c>
       <c r="O9">
-        <v>0.2958877205940386</v>
+        <v>0.2699522716772689</v>
       </c>
       <c r="P9">
-        <v>1.444628282900306</v>
+        <v>1.318002267600783</v>
       </c>
       <c r="Q9">
-        <v>1.479628282900306</v>
+        <v>1.353002267600783</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09021235780364101</v>
+        <v>0.09061785998588165</v>
       </c>
       <c r="T9">
-        <v>1.025689556666074</v>
+        <v>1.035054503138144</v>
       </c>
       <c r="U9">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V9">
         <v>0.17</v>
       </c>
       <c r="W9">
-        <v>0.047974</v>
+        <v>0.053203</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.050946238904864</v>
+        <v>3.196202902224859</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08762467118701112</v>
+        <v>0.0882102996166361</v>
       </c>
       <c r="C10">
-        <v>129.5217808089195</v>
+        <v>126.1690798216327</v>
       </c>
       <c r="D10">
-        <v>140.6877411945973</v>
+        <v>138.7450352555202</v>
       </c>
       <c r="E10">
-        <v>10.28045556470518</v>
+        <v>11.6904506129149</v>
       </c>
       <c r="F10">
-        <v>11.27996038567781</v>
+        <v>12.68995543388754</v>
       </c>
       <c r="G10">
         <v>0.114</v>
@@ -2089,45 +2089,45 @@
         <v>2.311</v>
       </c>
       <c r="M10">
-        <v>0.7230454607219479</v>
+        <v>0.912407795696514</v>
       </c>
       <c r="N10">
-        <v>1.587954539278052</v>
+        <v>1.398592204303486</v>
       </c>
       <c r="O10">
-        <v>0.2699522716772689</v>
+        <v>0.2377606747315926</v>
       </c>
       <c r="P10">
-        <v>1.318002267600783</v>
+        <v>1.160831529571893</v>
       </c>
       <c r="Q10">
-        <v>1.353002267600783</v>
+        <v>1.195831529571893</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09061785998588165</v>
+        <v>0.09103227430399571</v>
       </c>
       <c r="T10">
-        <v>1.035054503138144</v>
+        <v>1.044625272609601</v>
       </c>
       <c r="U10">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V10">
         <v>0.17</v>
       </c>
       <c r="W10">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.196202902224859</v>
+        <v>2.532858674487572</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0882102996166361</v>
+        <v>0.08860170804626109</v>
       </c>
       <c r="C11">
-        <v>126.1690798216327</v>
+        <v>123.4903041838976</v>
       </c>
       <c r="D11">
-        <v>138.7450352555202</v>
+        <v>137.4762546659948</v>
       </c>
       <c r="E11">
-        <v>11.6904506129149</v>
+        <v>13.10044566112463</v>
       </c>
       <c r="F11">
-        <v>12.68995543388754</v>
+        <v>14.09995048209726</v>
       </c>
       <c r="G11">
         <v>0.114</v>
@@ -2171,45 +2171,45 @@
         <v>2.311</v>
       </c>
       <c r="M11">
-        <v>0.912407795696514</v>
+        <v>1.068776246542973</v>
       </c>
       <c r="N11">
-        <v>1.398592204303486</v>
+        <v>1.242223753457027</v>
       </c>
       <c r="O11">
-        <v>0.2377606747315926</v>
+        <v>0.2111780380876946</v>
       </c>
       <c r="P11">
-        <v>1.160831529571893</v>
+        <v>1.031045715369333</v>
       </c>
       <c r="Q11">
-        <v>1.195831529571893</v>
+        <v>1.066045715369333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09103227430399571</v>
+        <v>0.09145589782917898</v>
       </c>
       <c r="T11">
-        <v>1.044625272609601</v>
+        <v>1.054408725847089</v>
       </c>
       <c r="U11">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V11">
         <v>0.17</v>
       </c>
       <c r="W11">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.532858674487572</v>
+        <v>2.162286079499879</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08860170804626109</v>
+        <v>0.08999824647588606</v>
       </c>
       <c r="C12">
-        <v>123.4903041838976</v>
+        <v>117.7364518990276</v>
       </c>
       <c r="D12">
-        <v>137.4762546659948</v>
+        <v>133.1323974293346</v>
       </c>
       <c r="E12">
-        <v>13.10044566112463</v>
+        <v>14.51044070933436</v>
       </c>
       <c r="F12">
-        <v>14.09995048209726</v>
+        <v>15.50994553030699</v>
       </c>
       <c r="G12">
         <v>0.114</v>
@@ -2253,45 +2253,45 @@
         <v>2.311</v>
       </c>
       <c r="M12">
-        <v>1.068776246542973</v>
+        <v>1.395895097727629</v>
       </c>
       <c r="N12">
-        <v>1.242223753457027</v>
+        <v>0.9151049022723707</v>
       </c>
       <c r="O12">
-        <v>0.2111780380876946</v>
+        <v>0.155567833386303</v>
       </c>
       <c r="P12">
-        <v>1.031045715369332</v>
+        <v>0.7595370688860676</v>
       </c>
       <c r="Q12">
-        <v>1.066045715369332</v>
+        <v>0.7945370688860677</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09145589782917898</v>
+        <v>0.09188904098414163</v>
       </c>
       <c r="T12">
-        <v>1.054408725847089</v>
+        <v>1.06441203196632</v>
       </c>
       <c r="U12">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V12">
         <v>0.17</v>
       </c>
       <c r="W12">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>2.162286079499878</v>
+        <v>1.655568533596877</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08999824647588606</v>
+        <v>0.09021618490551105</v>
       </c>
       <c r="C13">
-        <v>117.7364518990276</v>
+        <v>115.6732115149188</v>
       </c>
       <c r="D13">
-        <v>133.1323974293346</v>
+        <v>132.4791520934355</v>
       </c>
       <c r="E13">
-        <v>14.51044070933436</v>
+        <v>15.92043575754408</v>
       </c>
       <c r="F13">
-        <v>15.50994553030699</v>
+        <v>16.91994057851672</v>
       </c>
       <c r="G13">
         <v>0.114</v>
@@ -2335,28 +2335,28 @@
         <v>2.311</v>
       </c>
       <c r="M13">
-        <v>1.395895097727629</v>
+        <v>1.522794652066504</v>
       </c>
       <c r="N13">
-        <v>0.9151049022723707</v>
+        <v>0.7882053479334956</v>
       </c>
       <c r="O13">
-        <v>0.155567833386303</v>
+        <v>0.1339949091486943</v>
       </c>
       <c r="P13">
-        <v>0.7595370688860676</v>
+        <v>0.6542104387848013</v>
       </c>
       <c r="Q13">
-        <v>0.7945370688860677</v>
+        <v>0.6892104387848014</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09188904098414163</v>
+        <v>0.09233202830171709</v>
       </c>
       <c r="T13">
-        <v>1.06441203196632</v>
+        <v>1.074642685951896</v>
       </c>
       <c r="U13">
         <v>0.09</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>1.655568533596877</v>
+        <v>1.517604489130471</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09021618490551105</v>
+        <v>0.09715120390481886</v>
       </c>
       <c r="C14">
-        <v>115.6732115149188</v>
+        <v>96.37180658889801</v>
       </c>
       <c r="D14">
-        <v>132.4791520934355</v>
+        <v>114.5877422156244</v>
       </c>
       <c r="E14">
-        <v>15.92043575754408</v>
+        <v>17.33043080575381</v>
       </c>
       <c r="F14">
-        <v>16.91994057851672</v>
+        <v>18.32993562672645</v>
       </c>
       <c r="G14">
         <v>0.114</v>
@@ -2417,45 +2417,45 @@
         <v>2.311</v>
       </c>
       <c r="M14">
-        <v>1.522794652066504</v>
+        <v>2.690834550003443</v>
       </c>
       <c r="N14">
-        <v>0.7882053479334956</v>
+        <v>-0.3798345500034426</v>
       </c>
       <c r="O14">
-        <v>0.1339949091486943</v>
+        <v>-0.06457187350058524</v>
       </c>
       <c r="P14">
-        <v>0.6542104387848013</v>
+        <v>-0.3152626765028573</v>
       </c>
       <c r="Q14">
-        <v>0.6892104387848014</v>
+        <v>-0.2802626765028573</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09233202830171709</v>
+        <v>0.09293508706535908</v>
       </c>
       <c r="T14">
-        <v>1.074642685951896</v>
+        <v>1.088570140077577</v>
       </c>
       <c r="U14">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V14">
-        <v>0.17</v>
+        <v>0.1460030309182322</v>
       </c>
       <c r="W14">
-        <v>0.07469999999999999</v>
+        <v>0.1253667550612035</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y14">
-        <v>1.517604489130471</v>
+        <v>0.8588413583425423</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09715120390481886</v>
+        <v>0.1059345679096497</v>
       </c>
       <c r="C15">
-        <v>96.37180658889801</v>
+        <v>78.22491818038782</v>
       </c>
       <c r="D15">
-        <v>114.5877422156244</v>
+        <v>97.85084885532399</v>
       </c>
       <c r="E15">
-        <v>17.33043080575381</v>
+        <v>18.74042585396354</v>
       </c>
       <c r="F15">
-        <v>18.32993562672645</v>
+        <v>19.73993067493617</v>
       </c>
       <c r="G15">
         <v>0.114</v>
@@ -2499,45 +2499,45 @@
         <v>2.311</v>
       </c>
       <c r="M15">
-        <v>2.690834550003443</v>
+        <v>3.963778079527184</v>
       </c>
       <c r="N15">
-        <v>-0.3798345500034426</v>
+        <v>-1.652778079527184</v>
       </c>
       <c r="O15">
-        <v>-0.06457187350058524</v>
+        <v>-0.2809722735196212</v>
       </c>
       <c r="P15">
-        <v>-0.3152626765028573</v>
+        <v>-1.371805806007562</v>
       </c>
       <c r="Q15">
-        <v>-0.2802626765028573</v>
+        <v>-1.336805806007562</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09293508706535908</v>
+        <v>0.09373126715313171</v>
       </c>
       <c r="T15">
-        <v>1.088570140077577</v>
+        <v>1.106957670973019</v>
       </c>
       <c r="U15">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V15">
-        <v>0.1460030309182322</v>
+        <v>0.09911503422181074</v>
       </c>
       <c r="W15">
-        <v>0.1253667550612035</v>
+        <v>0.1808977011282604</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y15">
-        <v>0.8588413583425423</v>
+        <v>0.5830296130694749</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1059345679096497</v>
+        <v>0.1074845679096497</v>
       </c>
       <c r="C16">
-        <v>78.22491818038782</v>
+        <v>74.35614258356657</v>
       </c>
       <c r="D16">
-        <v>97.85084885532399</v>
+        <v>95.39206830671246</v>
       </c>
       <c r="E16">
-        <v>18.74042585396354</v>
+        <v>20.15042090217326</v>
       </c>
       <c r="F16">
-        <v>19.73993067493617</v>
+        <v>21.1499257231459</v>
       </c>
       <c r="G16">
         <v>0.114</v>
@@ -2581,37 +2581,37 @@
         <v>2.311</v>
       </c>
       <c r="M16">
-        <v>3.963778079527184</v>
+        <v>4.246905085207697</v>
       </c>
       <c r="N16">
-        <v>-1.652778079527184</v>
+        <v>-1.935905085207697</v>
       </c>
       <c r="O16">
-        <v>-0.2809722735196212</v>
+        <v>-0.3291038644853085</v>
       </c>
       <c r="P16">
-        <v>-1.371805806007562</v>
+        <v>-1.606801220722388</v>
       </c>
       <c r="Q16">
-        <v>-1.336805806007562</v>
+        <v>-1.571801220722388</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09373126715313171</v>
+        <v>0.09429516441375679</v>
       </c>
       <c r="T16">
-        <v>1.106957670973019</v>
+        <v>1.119980702396231</v>
       </c>
       <c r="U16">
         <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.09911503422181074</v>
+        <v>0.09250736527369001</v>
       </c>
       <c r="W16">
-        <v>0.1808977011282604</v>
+        <v>0.1822245210530431</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.5830296130694749</v>
+        <v>0.5441609721981765</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1074845679096497</v>
+        <v>0.1090345679096497</v>
       </c>
       <c r="C17">
-        <v>74.35614258356658</v>
+        <v>70.60790579886449</v>
       </c>
       <c r="D17">
-        <v>95.39206830671247</v>
+        <v>93.05382657022011</v>
       </c>
       <c r="E17">
-        <v>20.15042090217326</v>
+        <v>21.56041595038299</v>
       </c>
       <c r="F17">
-        <v>21.14992572314589</v>
+        <v>22.55992077135562</v>
       </c>
       <c r="G17">
         <v>0.114</v>
@@ -2663,37 +2663,37 @@
         <v>2.311</v>
       </c>
       <c r="M17">
-        <v>4.246905085207696</v>
+        <v>4.530032090888209</v>
       </c>
       <c r="N17">
-        <v>-1.935905085207696</v>
+        <v>-2.219032090888209</v>
       </c>
       <c r="O17">
-        <v>-0.3291038644853083</v>
+        <v>-0.3772354554509956</v>
       </c>
       <c r="P17">
-        <v>-1.606801220722388</v>
+        <v>-1.841796635437214</v>
       </c>
       <c r="Q17">
-        <v>-1.571801220722388</v>
+        <v>-1.806796635437214</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09429516441375679</v>
+        <v>0.09487248779963485</v>
       </c>
       <c r="T17">
-        <v>1.119980702396231</v>
+        <v>1.133313805996186</v>
       </c>
       <c r="U17">
         <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.09250736527369002</v>
+        <v>0.08672565494408441</v>
       </c>
       <c r="W17">
-        <v>0.182224521053043</v>
+        <v>0.1833854884872279</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.5441609721981766</v>
+        <v>0.5101509114357905</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1090345679096497</v>
+        <v>0.1166206628627504</v>
       </c>
       <c r="C18">
-        <v>70.60790579886449</v>
+        <v>59.23026662567523</v>
       </c>
       <c r="D18">
-        <v>93.05382657022011</v>
+        <v>83.08618244524058</v>
       </c>
       <c r="E18">
-        <v>21.56041595038299</v>
+        <v>22.97041099859272</v>
       </c>
       <c r="F18">
-        <v>22.55992077135562</v>
+        <v>23.96991581956535</v>
       </c>
       <c r="G18">
         <v>0.114</v>
@@ -2745,45 +2745,45 @@
         <v>2.311</v>
       </c>
       <c r="M18">
-        <v>4.530032090888209</v>
+        <v>5.65210615025351</v>
       </c>
       <c r="N18">
-        <v>-2.219032090888209</v>
+        <v>-3.34110615025351</v>
       </c>
       <c r="O18">
-        <v>-0.3772354554509956</v>
+        <v>-0.5679880455430968</v>
       </c>
       <c r="P18">
-        <v>-1.841796635437214</v>
+        <v>-2.773118104710413</v>
       </c>
       <c r="Q18">
-        <v>-1.806796635437214</v>
+        <v>-2.738118104710413</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09487248779963485</v>
+        <v>0.09556745145155893</v>
       </c>
       <c r="T18">
-        <v>1.133313805996186</v>
+        <v>1.149363774862793</v>
       </c>
       <c r="U18">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.08672565494408441</v>
+        <v>0.06950860255559406</v>
       </c>
       <c r="W18">
-        <v>0.1833854884872279</v>
+        <v>0.2194098715173909</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y18">
-        <v>0.5101509114357905</v>
+        <v>0.408874132679965</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1166206628627504</v>
+        <v>0.1185206628627504</v>
       </c>
       <c r="C19">
-        <v>59.23026662567523</v>
+        <v>55.64944776437812</v>
       </c>
       <c r="D19">
-        <v>83.08618244524058</v>
+        <v>80.9153586321532</v>
       </c>
       <c r="E19">
-        <v>22.97041099859272</v>
+        <v>24.38040604680245</v>
       </c>
       <c r="F19">
-        <v>23.96991581956535</v>
+        <v>25.37991086777508</v>
       </c>
       <c r="G19">
         <v>0.114</v>
@@ -2827,37 +2827,37 @@
         <v>2.311</v>
       </c>
       <c r="M19">
-        <v>5.65210615025351</v>
+        <v>5.984582982621364</v>
       </c>
       <c r="N19">
-        <v>-3.34110615025351</v>
+        <v>-3.673582982621364</v>
       </c>
       <c r="O19">
-        <v>-0.5679880455430968</v>
+        <v>-0.624509107045632</v>
       </c>
       <c r="P19">
-        <v>-2.773118104710413</v>
+        <v>-3.049073875575732</v>
       </c>
       <c r="Q19">
-        <v>-2.738118104710413</v>
+        <v>-3.014073875575732</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09556745145155893</v>
+        <v>0.09617437159121209</v>
       </c>
       <c r="T19">
-        <v>1.149363774862793</v>
+        <v>1.163380406263558</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.06950860255559406</v>
+        <v>0.06564701352472771</v>
       </c>
       <c r="W19">
-        <v>0.2194098715173909</v>
+        <v>0.2203204342108692</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.408874132679965</v>
+        <v>0.3861589030866336</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1185206628627504</v>
+        <v>0.1204206628627504</v>
       </c>
       <c r="C20">
-        <v>55.64944776437813</v>
+        <v>52.17917644009374</v>
       </c>
       <c r="D20">
-        <v>80.9153586321532</v>
+        <v>78.85508235607854</v>
       </c>
       <c r="E20">
-        <v>24.38040604680244</v>
+        <v>25.79040109501217</v>
       </c>
       <c r="F20">
-        <v>25.37991086777507</v>
+        <v>26.7899059159848</v>
       </c>
       <c r="G20">
         <v>0.114</v>
@@ -2909,37 +2909,37 @@
         <v>2.311</v>
       </c>
       <c r="M20">
-        <v>5.984582982621363</v>
+        <v>6.317059814989217</v>
       </c>
       <c r="N20">
-        <v>-3.673582982621363</v>
+        <v>-4.006059814989217</v>
       </c>
       <c r="O20">
-        <v>-0.6245091070456317</v>
+        <v>-0.6810301685481669</v>
       </c>
       <c r="P20">
-        <v>-3.049073875575731</v>
+        <v>-3.32502964644105</v>
       </c>
       <c r="Q20">
-        <v>-3.014073875575731</v>
+        <v>-3.29002964644105</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09617437159121209</v>
+        <v>0.0967962774133258</v>
       </c>
       <c r="T20">
-        <v>1.163380406263558</v>
+        <v>1.177743127328541</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.06564701352472774</v>
+        <v>0.06219190754974205</v>
       </c>
       <c r="W20">
-        <v>0.2203204342108692</v>
+        <v>0.2211351481997708</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3861589030866337</v>
+        <v>0.3658347502926003</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1204206628627504</v>
+        <v>0.1223206628627504</v>
       </c>
       <c r="C21">
-        <v>52.17917644009374</v>
+        <v>48.81121800171736</v>
       </c>
       <c r="D21">
-        <v>78.85508235607854</v>
+        <v>76.89711896591189</v>
       </c>
       <c r="E21">
-        <v>25.79040109501217</v>
+        <v>27.20039614322189</v>
       </c>
       <c r="F21">
-        <v>26.7899059159848</v>
+        <v>28.19990096419453</v>
       </c>
       <c r="G21">
         <v>0.114</v>
@@ -2991,37 +2991,37 @@
         <v>2.311</v>
       </c>
       <c r="M21">
-        <v>6.317059814989217</v>
+        <v>6.649536647357071</v>
       </c>
       <c r="N21">
-        <v>-4.006059814989217</v>
+        <v>-4.338536647357071</v>
       </c>
       <c r="O21">
-        <v>-0.6810301685481669</v>
+        <v>-0.737551230050702</v>
       </c>
       <c r="P21">
-        <v>-3.32502964644105</v>
+        <v>-3.600985417306369</v>
       </c>
       <c r="Q21">
-        <v>-3.29002964644105</v>
+        <v>-3.565985417306369</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0967962774133258</v>
+        <v>0.09743373088099239</v>
       </c>
       <c r="T21">
-        <v>1.177743127328541</v>
+        <v>1.192464916420147</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.06219190754974205</v>
+        <v>0.05908231217225495</v>
       </c>
       <c r="W21">
-        <v>0.2211351481997708</v>
+        <v>0.2218683907897823</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3658347502926003</v>
+        <v>0.3475430127779703</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1223206628627504</v>
+        <v>0.1242206628627504</v>
       </c>
       <c r="C22">
-        <v>48.81121800171736</v>
+        <v>45.53813584480847</v>
       </c>
       <c r="D22">
-        <v>76.89711896591189</v>
+        <v>75.03403185721272</v>
       </c>
       <c r="E22">
-        <v>27.20039614322189</v>
+        <v>28.61039119143162</v>
       </c>
       <c r="F22">
-        <v>28.19990096419453</v>
+        <v>29.60989601240426</v>
       </c>
       <c r="G22">
         <v>0.114</v>
@@ -3073,37 +3073,37 @@
         <v>2.311</v>
       </c>
       <c r="M22">
-        <v>6.649536647357071</v>
+        <v>6.982013479724925</v>
       </c>
       <c r="N22">
-        <v>-4.338536647357071</v>
+        <v>-4.671013479724925</v>
       </c>
       <c r="O22">
-        <v>-0.737551230050702</v>
+        <v>-0.7940722915532373</v>
       </c>
       <c r="P22">
-        <v>-3.600985417306369</v>
+        <v>-3.876941188171688</v>
       </c>
       <c r="Q22">
-        <v>-3.565985417306369</v>
+        <v>-3.841941188171687</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09743373088099239</v>
+        <v>0.09808732241113154</v>
       </c>
       <c r="T22">
-        <v>1.192464916420147</v>
+        <v>1.207559409033061</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.05908231217225495</v>
+        <v>0.0562688687354809</v>
       </c>
       <c r="W22">
-        <v>0.2218683907897823</v>
+        <v>0.2225318007521736</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3475430127779703</v>
+        <v>0.3309933455028288</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1242206628627504</v>
+        <v>0.1261206628627504</v>
       </c>
       <c r="C23">
-        <v>45.5381358448085</v>
+        <v>42.3531970218902</v>
       </c>
       <c r="D23">
-        <v>75.03403185721275</v>
+        <v>73.25908808250418</v>
       </c>
       <c r="E23">
-        <v>28.61039119143162</v>
+        <v>30.02038623964135</v>
       </c>
       <c r="F23">
-        <v>29.60989601240426</v>
+        <v>31.01989106061398</v>
       </c>
       <c r="G23">
         <v>0.114</v>
@@ -3155,37 +3155,37 @@
         <v>2.311</v>
       </c>
       <c r="M23">
-        <v>6.982013479724924</v>
+        <v>7.314490312092778</v>
       </c>
       <c r="N23">
-        <v>-4.671013479724924</v>
+        <v>-5.003490312092778</v>
       </c>
       <c r="O23">
-        <v>-0.7940722915532371</v>
+        <v>-0.8505933530557722</v>
       </c>
       <c r="P23">
-        <v>-3.876941188171687</v>
+        <v>-4.152896959037006</v>
       </c>
       <c r="Q23">
-        <v>-3.841941188171687</v>
+        <v>-4.117896959037005</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09808732241113152</v>
+        <v>0.09875767269845373</v>
       </c>
       <c r="T23">
-        <v>1.207559409033061</v>
+        <v>1.2230409399181</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.05626886873548091</v>
+        <v>0.05371119288386814</v>
       </c>
       <c r="W23">
-        <v>0.2225318007521736</v>
+        <v>0.2231349007179839</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3309933455028288</v>
+        <v>0.3159481934345184</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1261206628627504</v>
+        <v>0.1280206628627504</v>
       </c>
       <c r="C24">
-        <v>42.3531970218902</v>
+        <v>39.25029094000138</v>
       </c>
       <c r="D24">
-        <v>73.25908808250418</v>
+        <v>71.56617704882508</v>
       </c>
       <c r="E24">
-        <v>30.02038623964135</v>
+        <v>31.43038128785107</v>
       </c>
       <c r="F24">
-        <v>31.01989106061398</v>
+        <v>32.42988610882371</v>
       </c>
       <c r="G24">
         <v>0.114</v>
@@ -3237,37 +3237,37 @@
         <v>2.311</v>
       </c>
       <c r="M24">
-        <v>7.314490312092778</v>
+        <v>7.646967144460631</v>
       </c>
       <c r="N24">
-        <v>-5.003490312092778</v>
+        <v>-5.335967144460631</v>
       </c>
       <c r="O24">
-        <v>-0.8505933530557722</v>
+        <v>-0.9071144145583073</v>
       </c>
       <c r="P24">
-        <v>-4.152896959037006</v>
+        <v>-4.428852729902323</v>
       </c>
       <c r="Q24">
-        <v>-4.117896959037005</v>
+        <v>-4.393852729902323</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09875767269845373</v>
+        <v>0.09944543468155054</v>
       </c>
       <c r="T24">
-        <v>1.2230409399181</v>
+        <v>1.238924588488465</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.05371119288386814</v>
+        <v>0.05137592362804778</v>
       </c>
       <c r="W24">
-        <v>0.2231349007179839</v>
+        <v>0.2236855572085064</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3159481934345184</v>
+        <v>0.3022113154591046</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1280206628627504</v>
+        <v>0.1299206628627504</v>
       </c>
       <c r="C25">
-        <v>39.25029094000138</v>
+        <v>36.22385907632546</v>
       </c>
       <c r="D25">
-        <v>71.56617704882508</v>
+        <v>69.9497402333589</v>
       </c>
       <c r="E25">
-        <v>31.43038128785107</v>
+        <v>32.84037633606081</v>
       </c>
       <c r="F25">
-        <v>32.42988610882371</v>
+        <v>33.83988115703344</v>
       </c>
       <c r="G25">
         <v>0.114</v>
@@ -3319,37 +3319,37 @@
         <v>2.311</v>
       </c>
       <c r="M25">
-        <v>7.646967144460631</v>
+        <v>7.979443976828485</v>
       </c>
       <c r="N25">
-        <v>-5.335967144460631</v>
+        <v>-5.668443976828486</v>
       </c>
       <c r="O25">
-        <v>-0.9071144145583073</v>
+        <v>-0.9636354760608427</v>
       </c>
       <c r="P25">
-        <v>-4.428852729902323</v>
+        <v>-4.704808500767643</v>
       </c>
       <c r="Q25">
-        <v>-4.393852729902323</v>
+        <v>-4.669808500767643</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09944543468155054</v>
+        <v>0.1001512956642025</v>
       </c>
       <c r="T25">
-        <v>1.238924588488465</v>
+        <v>1.255226227810681</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.05137592362804778</v>
+        <v>0.04923526014354579</v>
       </c>
       <c r="W25">
-        <v>0.2236855572085064</v>
+        <v>0.2241903256581519</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3022113154591046</v>
+        <v>0.2896191773149752</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1299206628627504</v>
+        <v>0.1318206628627504</v>
       </c>
       <c r="C26">
-        <v>36.22385907632548</v>
+        <v>33.26883400834671</v>
       </c>
       <c r="D26">
-        <v>69.94974023335891</v>
+        <v>68.40471021358987</v>
       </c>
       <c r="E26">
-        <v>32.8403763360608</v>
+        <v>34.25037138427053</v>
       </c>
       <c r="F26">
-        <v>33.83988115703343</v>
+        <v>35.24987620524316</v>
       </c>
       <c r="G26">
         <v>0.114</v>
@@ -3401,37 +3401,37 @@
         <v>2.311</v>
       </c>
       <c r="M26">
-        <v>7.979443976828484</v>
+        <v>8.311920809196337</v>
       </c>
       <c r="N26">
-        <v>-5.668443976828484</v>
+        <v>-6.000920809196337</v>
       </c>
       <c r="O26">
-        <v>-0.9636354760608423</v>
+        <v>-1.020156537563377</v>
       </c>
       <c r="P26">
-        <v>-4.704808500767641</v>
+        <v>-4.98076427163296</v>
       </c>
       <c r="Q26">
-        <v>-4.669808500767641</v>
+        <v>-4.94576427163296</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1001512956642025</v>
+        <v>0.1008759796063919</v>
       </c>
       <c r="T26">
-        <v>1.255226227810681</v>
+        <v>1.271962577514824</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.0492352601435458</v>
+        <v>0.04726584973780396</v>
       </c>
       <c r="W26">
-        <v>0.2241903256581519</v>
+        <v>0.2246547126318258</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2896191773149752</v>
+        <v>0.2780344102223763</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1318206628627504</v>
+        <v>0.1337206628627504</v>
       </c>
       <c r="C27">
-        <v>33.26883400834671</v>
+        <v>30.38058634949968</v>
       </c>
       <c r="D27">
-        <v>68.40471021358987</v>
+        <v>66.92645760295257</v>
       </c>
       <c r="E27">
-        <v>34.25037138427053</v>
+        <v>35.66036643248026</v>
       </c>
       <c r="F27">
-        <v>35.24987620524316</v>
+        <v>36.65987125345289</v>
       </c>
       <c r="G27">
         <v>0.114</v>
@@ -3483,37 +3483,37 @@
         <v>2.311</v>
       </c>
       <c r="M27">
-        <v>8.311920809196337</v>
+        <v>8.644397641564192</v>
       </c>
       <c r="N27">
-        <v>-6.000920809196337</v>
+        <v>-6.333397641564192</v>
       </c>
       <c r="O27">
-        <v>-1.020156537563377</v>
+        <v>-1.076677599065913</v>
       </c>
       <c r="P27">
-        <v>-4.98076427163296</v>
+        <v>-5.256720042498279</v>
       </c>
       <c r="Q27">
-        <v>-4.94576427163296</v>
+        <v>-5.221720042498279</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1008759796063919</v>
+        <v>0.1016202496010729</v>
       </c>
       <c r="T27">
-        <v>1.271962577514824</v>
+        <v>1.289151260994754</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.04726584973780396</v>
+        <v>0.04544793244019611</v>
       </c>
       <c r="W27">
-        <v>0.2246547126318258</v>
+        <v>0.2250833775306018</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2780344102223763</v>
+        <v>0.2673407790599771</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1337206628627504</v>
+        <v>0.1356206628627504</v>
       </c>
       <c r="C28">
-        <v>30.38058634949968</v>
+        <v>27.55487841972378</v>
       </c>
       <c r="D28">
-        <v>66.92645760295257</v>
+        <v>65.51074472138639</v>
       </c>
       <c r="E28">
-        <v>35.66036643248026</v>
+        <v>37.07036148068998</v>
       </c>
       <c r="F28">
-        <v>36.65987125345289</v>
+        <v>38.06986630166261</v>
       </c>
       <c r="G28">
         <v>0.114</v>
@@ -3565,37 +3565,37 @@
         <v>2.311</v>
       </c>
       <c r="M28">
-        <v>8.644397641564192</v>
+        <v>8.976874473932044</v>
       </c>
       <c r="N28">
-        <v>-6.333397641564192</v>
+        <v>-6.665874473932044</v>
       </c>
       <c r="O28">
-        <v>-1.076677599065913</v>
+        <v>-1.133198660568448</v>
       </c>
       <c r="P28">
-        <v>-5.256720042498279</v>
+        <v>-5.532675813363596</v>
       </c>
       <c r="Q28">
-        <v>-5.221720042498279</v>
+        <v>-5.497675813363596</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1016202496010729</v>
+        <v>0.1023849105545122</v>
       </c>
       <c r="T28">
-        <v>1.289151260994754</v>
+        <v>1.30681086730975</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.04544793244019611</v>
+        <v>0.04376467568315182</v>
       </c>
       <c r="W28">
-        <v>0.2250833775306018</v>
+        <v>0.2254802894739128</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2673407790599771</v>
+        <v>0.2574392687244225</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1356206628627504</v>
+        <v>0.1375206628627504</v>
       </c>
       <c r="C29">
-        <v>27.55487841972378</v>
+        <v>24.78782367432355</v>
       </c>
       <c r="D29">
-        <v>65.51074472138639</v>
+        <v>64.15368502419589</v>
       </c>
       <c r="E29">
-        <v>37.07036148068998</v>
+        <v>38.48035652889971</v>
       </c>
       <c r="F29">
-        <v>38.06986630166261</v>
+        <v>39.47986134987234</v>
       </c>
       <c r="G29">
         <v>0.114</v>
@@ -3647,37 +3647,37 @@
         <v>2.311</v>
       </c>
       <c r="M29">
-        <v>8.976874473932044</v>
+        <v>9.309351306299899</v>
       </c>
       <c r="N29">
-        <v>-6.665874473932044</v>
+        <v>-6.998351306299899</v>
       </c>
       <c r="O29">
-        <v>-1.133198660568448</v>
+        <v>-1.189719722070983</v>
       </c>
       <c r="P29">
-        <v>-5.532675813363596</v>
+        <v>-5.808631584228916</v>
       </c>
       <c r="Q29">
-        <v>-5.497675813363596</v>
+        <v>-5.773631584228916</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1023849105545122</v>
+        <v>0.1031708120899915</v>
       </c>
       <c r="T29">
-        <v>1.30681086730975</v>
+        <v>1.324961018244608</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.04376467568315182</v>
+        <v>0.04220165155161067</v>
       </c>
       <c r="W29">
-        <v>0.2254802894739128</v>
+        <v>0.2258488505641302</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2574392687244225</v>
+        <v>0.2482450091271217</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1375206628627504</v>
+        <v>0.1394206628627504</v>
       </c>
       <c r="C30">
-        <v>24.78782367432355</v>
+        <v>22.07585107309576</v>
       </c>
       <c r="D30">
-        <v>64.15368502419589</v>
+        <v>62.85170747117783</v>
       </c>
       <c r="E30">
-        <v>38.48035652889971</v>
+        <v>39.89035157710944</v>
       </c>
       <c r="F30">
-        <v>39.47986134987234</v>
+        <v>40.88985639808207</v>
       </c>
       <c r="G30">
         <v>0.114</v>
@@ -3729,37 +3729,37 @@
         <v>2.311</v>
       </c>
       <c r="M30">
-        <v>9.309351306299899</v>
+        <v>9.641828138667753</v>
       </c>
       <c r="N30">
-        <v>-6.998351306299899</v>
+        <v>-7.330828138667753</v>
       </c>
       <c r="O30">
-        <v>-1.189719722070983</v>
+        <v>-1.246240783573518</v>
       </c>
       <c r="P30">
-        <v>-5.808631584228916</v>
+        <v>-6.084587355094235</v>
       </c>
       <c r="Q30">
-        <v>-5.773631584228916</v>
+        <v>-6.049587355094235</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1031708120899915</v>
+        <v>0.1039788516968928</v>
       </c>
       <c r="T30">
-        <v>1.324961018244608</v>
+        <v>1.343622441036786</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.04220165155161067</v>
+        <v>0.04074642218776203</v>
       </c>
       <c r="W30">
-        <v>0.2258488505641302</v>
+        <v>0.2261919936481257</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2482450091271217</v>
+        <v>0.2396848363986002</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1394206628627504</v>
+        <v>0.1413206628627504</v>
       </c>
       <c r="C31">
-        <v>22.07585107309578</v>
+        <v>19.41567370185482</v>
       </c>
       <c r="D31">
-        <v>62.85170747117785</v>
+        <v>61.60152514814661</v>
       </c>
       <c r="E31">
-        <v>39.89035157710943</v>
+        <v>41.30034662531916</v>
       </c>
       <c r="F31">
-        <v>40.88985639808207</v>
+        <v>42.29985144629179</v>
       </c>
       <c r="G31">
         <v>0.114</v>
@@ -3811,37 +3811,37 @@
         <v>2.311</v>
       </c>
       <c r="M31">
-        <v>9.641828138667751</v>
+        <v>9.974304971035604</v>
       </c>
       <c r="N31">
-        <v>-7.330828138667751</v>
+        <v>-7.663304971035604</v>
       </c>
       <c r="O31">
-        <v>-1.246240783573518</v>
+        <v>-1.302761845076053</v>
       </c>
       <c r="P31">
-        <v>-6.084587355094234</v>
+        <v>-6.360543125959551</v>
       </c>
       <c r="Q31">
-        <v>-6.049587355094234</v>
+        <v>-6.325543125959551</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1039788516968928</v>
+        <v>0.1048099781497056</v>
       </c>
       <c r="T31">
-        <v>1.343622441036786</v>
+        <v>1.362817047337311</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.04074642218776204</v>
+        <v>0.03938820811483664</v>
       </c>
       <c r="W31">
-        <v>0.2261919936481257</v>
+        <v>0.2265122605265215</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2396848363986002</v>
+        <v>0.2316953418519803</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1413206628627504</v>
+        <v>0.1432206628627504</v>
       </c>
       <c r="C32">
-        <v>19.41567370185482</v>
+        <v>16.80426106581391</v>
       </c>
       <c r="D32">
-        <v>61.60152514814661</v>
+        <v>60.40010756031543</v>
       </c>
       <c r="E32">
-        <v>41.30034662531916</v>
+        <v>42.71034167352889</v>
       </c>
       <c r="F32">
-        <v>42.29985144629179</v>
+        <v>43.70984649450152</v>
       </c>
       <c r="G32">
         <v>0.114</v>
@@ -3893,37 +3893,37 @@
         <v>2.311</v>
       </c>
       <c r="M32">
-        <v>9.974304971035604</v>
+        <v>10.30678180340346</v>
       </c>
       <c r="N32">
-        <v>-7.663304971035604</v>
+        <v>-7.995781803403458</v>
       </c>
       <c r="O32">
-        <v>-1.302761845076053</v>
+        <v>-1.359282906578588</v>
       </c>
       <c r="P32">
-        <v>-6.360543125959551</v>
+        <v>-6.63649889682487</v>
       </c>
       <c r="Q32">
-        <v>-6.325543125959551</v>
+        <v>-6.60149889682487</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1048099781497056</v>
+        <v>0.105665195224339</v>
       </c>
       <c r="T32">
-        <v>1.362817047337311</v>
+        <v>1.382568019037852</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.03938820811483664</v>
+        <v>0.03811762075629352</v>
       </c>
       <c r="W32">
-        <v>0.2265122605265215</v>
+        <v>0.226811865025666</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2316953418519803</v>
+        <v>0.2242212985664325</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1432206628627504</v>
+        <v>0.1451206628627504</v>
       </c>
       <c r="C33">
-        <v>16.80426106581391</v>
+        <v>14.23881456312503</v>
       </c>
       <c r="D33">
-        <v>60.40010756031543</v>
+        <v>59.24465610583628</v>
       </c>
       <c r="E33">
-        <v>42.71034167352889</v>
+        <v>44.12033672173862</v>
       </c>
       <c r="F33">
-        <v>43.70984649450152</v>
+        <v>45.11984154271125</v>
       </c>
       <c r="G33">
         <v>0.114</v>
@@ -3975,37 +3975,37 @@
         <v>2.311</v>
       </c>
       <c r="M33">
-        <v>10.30678180340346</v>
+        <v>10.63925863577131</v>
       </c>
       <c r="N33">
-        <v>-7.995781803403458</v>
+        <v>-8.328258635771313</v>
       </c>
       <c r="O33">
-        <v>-1.359282906578588</v>
+        <v>-1.415803968081123</v>
       </c>
       <c r="P33">
-        <v>-6.63649889682487</v>
+        <v>-6.91245466769019</v>
       </c>
       <c r="Q33">
-        <v>-6.60149889682487</v>
+        <v>-6.87745466769019</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.105665195224339</v>
+        <v>0.106545565742344</v>
       </c>
       <c r="T33">
-        <v>1.382568019037852</v>
+        <v>1.402899901670762</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.03811762075629352</v>
+        <v>0.03692644510765934</v>
       </c>
       <c r="W33">
-        <v>0.226811865025666</v>
+        <v>0.2270927442436139</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2242212985664325</v>
+        <v>0.2172143829862314</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1451206628627504</v>
+        <v>0.1470206628627504</v>
       </c>
       <c r="C34">
-        <v>14.23881456312503</v>
+        <v>11.71674572071657</v>
       </c>
       <c r="D34">
-        <v>59.24465610583628</v>
+        <v>58.13258231163755</v>
       </c>
       <c r="E34">
-        <v>44.12033672173862</v>
+        <v>45.53033176994834</v>
       </c>
       <c r="F34">
-        <v>45.11984154271125</v>
+        <v>46.52983659092097</v>
       </c>
       <c r="G34">
         <v>0.114</v>
@@ -4057,37 +4057,37 @@
         <v>2.311</v>
       </c>
       <c r="M34">
-        <v>10.63925863577131</v>
+        <v>10.97173546813917</v>
       </c>
       <c r="N34">
-        <v>-8.328258635771313</v>
+        <v>-8.660735468139166</v>
       </c>
       <c r="O34">
-        <v>-1.415803968081123</v>
+        <v>-1.472325029583658</v>
       </c>
       <c r="P34">
-        <v>-6.91245466769019</v>
+        <v>-7.188410438555508</v>
       </c>
       <c r="Q34">
-        <v>-6.87745466769019</v>
+        <v>-7.153410438555508</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.106545565742344</v>
+        <v>0.1074522159773043</v>
       </c>
       <c r="T34">
-        <v>1.402899901670762</v>
+        <v>1.42383870617331</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.03692644510765934</v>
+        <v>0.03580746192257876</v>
       </c>
       <c r="W34">
-        <v>0.2270927442436139</v>
+        <v>0.2273566004786559</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2172143829862314</v>
+        <v>0.2106321289563456</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1470206628627504</v>
+        <v>0.1489206628627504</v>
       </c>
       <c r="C35">
-        <v>11.71674572071657</v>
+        <v>9.235656836161773</v>
       </c>
       <c r="D35">
-        <v>58.13258231163755</v>
+        <v>57.06148847529248</v>
       </c>
       <c r="E35">
-        <v>45.53033176994834</v>
+        <v>46.94032681815807</v>
       </c>
       <c r="F35">
-        <v>46.52983659092097</v>
+        <v>47.9398316391307</v>
       </c>
       <c r="G35">
         <v>0.114</v>
@@ -4139,37 +4139,37 @@
         <v>2.311</v>
       </c>
       <c r="M35">
-        <v>10.97173546813917</v>
+        <v>11.30421230050702</v>
       </c>
       <c r="N35">
-        <v>-8.660735468139166</v>
+        <v>-8.99321230050702</v>
       </c>
       <c r="O35">
-        <v>-1.472325029583658</v>
+        <v>-1.528846091086193</v>
       </c>
       <c r="P35">
-        <v>-7.188410438555508</v>
+        <v>-7.464366209420827</v>
       </c>
       <c r="Q35">
-        <v>-7.153410438555508</v>
+        <v>-7.429366209420826</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1074522159773043</v>
+        <v>0.1083863404618089</v>
       </c>
       <c r="T35">
-        <v>1.42383870617331</v>
+        <v>1.445412019903209</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.03580746192257876</v>
+        <v>0.03475430127779703</v>
       </c>
       <c r="W35">
-        <v>0.2273566004786559</v>
+        <v>0.2276049357586955</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2106321289563456</v>
+        <v>0.2044370663399825</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1489206628627504</v>
+        <v>0.1508206628627504</v>
       </c>
       <c r="C36">
-        <v>9.235656836161773</v>
+        <v>6.793323720873339</v>
       </c>
       <c r="D36">
-        <v>57.06148847529248</v>
+        <v>56.02915040821377</v>
       </c>
       <c r="E36">
-        <v>46.94032681815807</v>
+        <v>48.3503218663678</v>
       </c>
       <c r="F36">
-        <v>47.9398316391307</v>
+        <v>49.34982668734043</v>
       </c>
       <c r="G36">
         <v>0.114</v>
@@ -4221,37 +4221,37 @@
         <v>2.311</v>
       </c>
       <c r="M36">
-        <v>11.30421230050702</v>
+        <v>11.63668913287487</v>
       </c>
       <c r="N36">
-        <v>-8.99321230050702</v>
+        <v>-9.325689132874874</v>
       </c>
       <c r="O36">
-        <v>-1.528846091086193</v>
+        <v>-1.585367152588729</v>
       </c>
       <c r="P36">
-        <v>-7.464366209420827</v>
+        <v>-7.740321980286145</v>
       </c>
       <c r="Q36">
-        <v>-7.429366209420826</v>
+        <v>-7.705321980286145</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1083863404618089</v>
+        <v>0.1093492072381445</v>
       </c>
       <c r="T36">
-        <v>1.445412019903209</v>
+        <v>1.46764912790172</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.03475430127779703</v>
+        <v>0.03376132124128854</v>
       </c>
       <c r="W36">
-        <v>0.2276049357586955</v>
+        <v>0.2278390804513042</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2044370663399825</v>
+        <v>0.1985960073016972</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1508206628627504</v>
+        <v>0.1527206628627504</v>
       </c>
       <c r="C37">
-        <v>6.793323720873339</v>
+        <v>4.387680283238083</v>
       </c>
       <c r="D37">
-        <v>56.02915040821377</v>
+        <v>55.03350201878825</v>
       </c>
       <c r="E37">
-        <v>48.3503218663678</v>
+        <v>49.76031691457753</v>
       </c>
       <c r="F37">
-        <v>49.34982668734043</v>
+        <v>50.75982173555016</v>
       </c>
       <c r="G37">
         <v>0.114</v>
@@ -4303,37 +4303,37 @@
         <v>2.311</v>
       </c>
       <c r="M37">
-        <v>11.63668913287487</v>
+        <v>11.96916596524273</v>
       </c>
       <c r="N37">
-        <v>-9.325689132874874</v>
+        <v>-9.658165965242729</v>
       </c>
       <c r="O37">
-        <v>-1.585367152588729</v>
+        <v>-1.641888214091264</v>
       </c>
       <c r="P37">
-        <v>-7.740321980286145</v>
+        <v>-8.016277751151465</v>
       </c>
       <c r="Q37">
-        <v>-7.705321980286145</v>
+        <v>-7.981277751151465</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1093492072381445</v>
+        <v>0.1103421636012405</v>
       </c>
       <c r="T37">
-        <v>1.46764912790172</v>
+        <v>1.490581145525184</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03376132124128854</v>
+        <v>0.03282350676236385</v>
       </c>
       <c r="W37">
-        <v>0.2278390804513042</v>
+        <v>0.2280602171054346</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1985960073016972</v>
+        <v>0.1930794515433167</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1527206628627504</v>
+        <v>0.1546206628627504</v>
       </c>
       <c r="C38">
-        <v>4.387680283238097</v>
+        <v>2.016804726814804</v>
       </c>
       <c r="D38">
-        <v>55.03350201878825</v>
+        <v>54.07262151057468</v>
       </c>
       <c r="E38">
-        <v>49.76031691457752</v>
+        <v>51.17031196278725</v>
       </c>
       <c r="F38">
-        <v>50.75982173555015</v>
+        <v>52.16981678375988</v>
       </c>
       <c r="G38">
         <v>0.114</v>
@@ -4385,37 +4385,37 @@
         <v>2.311</v>
       </c>
       <c r="M38">
-        <v>11.96916596524273</v>
+        <v>12.30164279761058</v>
       </c>
       <c r="N38">
-        <v>-9.658165965242725</v>
+        <v>-9.99064279761058</v>
       </c>
       <c r="O38">
-        <v>-1.641888214091263</v>
+        <v>-1.698409275593799</v>
       </c>
       <c r="P38">
-        <v>-8.016277751151462</v>
+        <v>-8.292233522016781</v>
       </c>
       <c r="Q38">
-        <v>-7.981277751151461</v>
+        <v>-8.257233522016781</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1103421636012405</v>
+        <v>0.1113666423885618</v>
       </c>
       <c r="T38">
-        <v>1.490581145525184</v>
+        <v>1.514241163708124</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03282350676236387</v>
+        <v>0.03193638495797566</v>
       </c>
       <c r="W38">
-        <v>0.2280602171054346</v>
+        <v>0.2282694004269094</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1930794515433168</v>
+        <v>0.1878610879880921</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1546206628627504</v>
+        <v>0.1565206628627504</v>
       </c>
       <c r="C39">
-        <v>2.016804726814804</v>
+        <v>-0.3210928304094196</v>
       </c>
       <c r="D39">
-        <v>54.07262151057468</v>
+        <v>53.14471900156019</v>
       </c>
       <c r="E39">
-        <v>51.17031196278725</v>
+        <v>52.58030701099698</v>
       </c>
       <c r="F39">
-        <v>52.16981678375988</v>
+        <v>53.57981183196961</v>
       </c>
       <c r="G39">
         <v>0.114</v>
@@ -4467,37 +4467,37 @@
         <v>2.311</v>
       </c>
       <c r="M39">
-        <v>12.30164279761058</v>
+        <v>12.63411962997843</v>
       </c>
       <c r="N39">
-        <v>-9.99064279761058</v>
+        <v>-10.32311962997843</v>
       </c>
       <c r="O39">
-        <v>-1.698409275593799</v>
+        <v>-1.754930337096334</v>
       </c>
       <c r="P39">
-        <v>-8.292233522016781</v>
+        <v>-8.568189292882099</v>
       </c>
       <c r="Q39">
-        <v>-8.257233522016781</v>
+        <v>-8.533189292882099</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1113666423885618</v>
+        <v>0.1124241688786999</v>
       </c>
       <c r="T39">
-        <v>1.514241163708124</v>
+        <v>1.538664408284061</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03193638495797566</v>
+        <v>0.03109595377487102</v>
       </c>
       <c r="W39">
-        <v>0.2282694004269094</v>
+        <v>0.2284675740998854</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1878610879880921</v>
+        <v>0.1829173751463001</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1565206628627504</v>
+        <v>0.1584206628627504</v>
       </c>
       <c r="C40">
-        <v>-0.3210928304094196</v>
+        <v>-2.627681483524675</v>
       </c>
       <c r="D40">
-        <v>53.14471900156019</v>
+        <v>52.24812539665466</v>
       </c>
       <c r="E40">
-        <v>52.58030701099698</v>
+        <v>53.99030205920671</v>
       </c>
       <c r="F40">
-        <v>53.57981183196961</v>
+        <v>54.98980688017934</v>
       </c>
       <c r="G40">
         <v>0.114</v>
@@ -4549,37 +4549,37 @@
         <v>2.311</v>
       </c>
       <c r="M40">
-        <v>12.63411962997843</v>
+        <v>12.96659646234629</v>
       </c>
       <c r="N40">
-        <v>-10.32311962997843</v>
+        <v>-10.65559646234629</v>
       </c>
       <c r="O40">
-        <v>-1.754930337096334</v>
+        <v>-1.811451398598869</v>
       </c>
       <c r="P40">
-        <v>-8.568189292882099</v>
+        <v>-8.844145063747419</v>
       </c>
       <c r="Q40">
-        <v>-8.533189292882099</v>
+        <v>-8.809145063747419</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1124241688786999</v>
+        <v>0.1135163683685146</v>
       </c>
       <c r="T40">
-        <v>1.538664408284061</v>
+        <v>1.563888414977243</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03109595377487102</v>
+        <v>0.03029862162679741</v>
       </c>
       <c r="W40">
-        <v>0.2284675740998854</v>
+        <v>0.2286555850204012</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1829173751463001</v>
+        <v>0.1782271860399848</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1584206628627504</v>
+        <v>0.1603206628627504</v>
       </c>
       <c r="C41">
-        <v>-2.627681483524675</v>
+        <v>-4.904519560512689</v>
       </c>
       <c r="D41">
-        <v>52.24812539665466</v>
+        <v>51.38128236787637</v>
       </c>
       <c r="E41">
-        <v>53.99030205920671</v>
+        <v>55.40029710741643</v>
       </c>
       <c r="F41">
-        <v>54.98980688017934</v>
+        <v>56.39980192838906</v>
       </c>
       <c r="G41">
         <v>0.114</v>
@@ -4631,37 +4631,37 @@
         <v>2.311</v>
       </c>
       <c r="M41">
-        <v>12.96659646234629</v>
+        <v>13.29907329471414</v>
       </c>
       <c r="N41">
-        <v>-10.65559646234629</v>
+        <v>-10.98807329471414</v>
       </c>
       <c r="O41">
-        <v>-1.811451398598869</v>
+        <v>-1.867972460101404</v>
       </c>
       <c r="P41">
-        <v>-8.844145063747419</v>
+        <v>-9.120100834612737</v>
       </c>
       <c r="Q41">
-        <v>-8.809145063747419</v>
+        <v>-9.085100834612737</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1135163683685146</v>
+        <v>0.1146449745079899</v>
       </c>
       <c r="T41">
-        <v>1.563888414977243</v>
+        <v>1.58995322189353</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.03029862162679741</v>
+        <v>0.02954115608612748</v>
       </c>
       <c r="W41">
-        <v>0.2286555850204012</v>
+        <v>0.2288341953948911</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1782271860399848</v>
+        <v>0.1737715063889851</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1603206628627504</v>
+        <v>0.1622206628627504</v>
       </c>
       <c r="C42">
-        <v>-4.904519560512689</v>
+        <v>-7.15306366091307</v>
       </c>
       <c r="D42">
-        <v>51.38128236787637</v>
+        <v>50.54273331568572</v>
       </c>
       <c r="E42">
-        <v>55.40029710741643</v>
+        <v>56.81029215562616</v>
       </c>
       <c r="F42">
-        <v>56.39980192838906</v>
+        <v>57.80979697659879</v>
       </c>
       <c r="G42">
         <v>0.114</v>
@@ -4713,37 +4713,37 @@
         <v>2.311</v>
       </c>
       <c r="M42">
-        <v>13.29907329471414</v>
+        <v>13.631550127082</v>
       </c>
       <c r="N42">
-        <v>-10.98807329471414</v>
+        <v>-11.320550127082</v>
       </c>
       <c r="O42">
-        <v>-1.867972460101404</v>
+        <v>-1.924493521603939</v>
       </c>
       <c r="P42">
-        <v>-9.120100834612737</v>
+        <v>-9.396056605478057</v>
       </c>
       <c r="Q42">
-        <v>-9.085100834612737</v>
+        <v>-9.361056605478057</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1146449745079899</v>
+        <v>0.1158118384827015</v>
       </c>
       <c r="T42">
-        <v>1.58995322189353</v>
+        <v>1.616901581586641</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.02954115608612748</v>
+        <v>0.0288206400840268</v>
       </c>
       <c r="W42">
-        <v>0.2288341953948911</v>
+        <v>0.2290040930681865</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1737715063889851</v>
+        <v>0.1695331769648636</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1622206628627504</v>
+        <v>0.1641206628627504</v>
       </c>
       <c r="C43">
-        <v>-7.15306366091307</v>
+        <v>-9.374676823629116</v>
       </c>
       <c r="D43">
-        <v>50.54273331568572</v>
+        <v>49.73111520117941</v>
       </c>
       <c r="E43">
-        <v>56.81029215562616</v>
+        <v>58.22028720383589</v>
       </c>
       <c r="F43">
-        <v>57.80979697659879</v>
+        <v>59.21979202480852</v>
       </c>
       <c r="G43">
         <v>0.114</v>
@@ -4795,37 +4795,37 @@
         <v>2.311</v>
       </c>
       <c r="M43">
-        <v>13.631550127082</v>
+        <v>13.96402695944985</v>
       </c>
       <c r="N43">
-        <v>-11.320550127082</v>
+        <v>-11.65302695944985</v>
       </c>
       <c r="O43">
-        <v>-1.924493521603939</v>
+        <v>-1.981014583106475</v>
       </c>
       <c r="P43">
-        <v>-9.396056605478057</v>
+        <v>-9.672012376343375</v>
       </c>
       <c r="Q43">
-        <v>-9.361056605478057</v>
+        <v>-9.637012376343375</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1158118384827015</v>
+        <v>0.1170189391461964</v>
       </c>
       <c r="T43">
-        <v>1.616901581586641</v>
+        <v>1.644779195062272</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.0288206400840268</v>
+        <v>0.02813443436774045</v>
       </c>
       <c r="W43">
-        <v>0.2290040930681865</v>
+        <v>0.2291659003760868</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1695331769648636</v>
+        <v>0.1654966727514144</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1641206628627504</v>
+        <v>0.1660206628627504</v>
       </c>
       <c r="C44">
-        <v>-9.374676823629109</v>
+        <v>-11.57063592021637</v>
       </c>
       <c r="D44">
-        <v>49.73111520117941</v>
+        <v>48.94515115280187</v>
       </c>
       <c r="E44">
-        <v>58.22028720383588</v>
+        <v>59.6302822520456</v>
       </c>
       <c r="F44">
-        <v>59.21979202480851</v>
+        <v>60.62978707301824</v>
       </c>
       <c r="G44">
         <v>0.114</v>
@@ -4877,37 +4877,37 @@
         <v>2.311</v>
       </c>
       <c r="M44">
-        <v>13.96402695944985</v>
+        <v>14.2965037918177</v>
       </c>
       <c r="N44">
-        <v>-11.65302695944985</v>
+        <v>-11.9855037918177</v>
       </c>
       <c r="O44">
-        <v>-1.981014583106474</v>
+        <v>-2.037535644609009</v>
       </c>
       <c r="P44">
-        <v>-9.672012376343375</v>
+        <v>-9.947968147208691</v>
       </c>
       <c r="Q44">
-        <v>-9.637012376343375</v>
+        <v>-9.912968147208691</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1170189391461964</v>
+        <v>0.1182683942189367</v>
       </c>
       <c r="T44">
-        <v>1.644779195062272</v>
+        <v>1.673634970414242</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.02813443436774045</v>
+        <v>0.02748014519639765</v>
       </c>
       <c r="W44">
-        <v>0.2291659003760868</v>
+        <v>0.2293201817626895</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1654966727514144</v>
+        <v>0.1616479129199861</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1660206628627504</v>
+        <v>0.1679206628627504</v>
       </c>
       <c r="C45">
-        <v>-11.57063592021637</v>
+        <v>-13.74213835800555</v>
       </c>
       <c r="D45">
-        <v>48.94515115280187</v>
+        <v>48.18364376322242</v>
       </c>
       <c r="E45">
-        <v>59.6302822520456</v>
+        <v>61.04027730025533</v>
       </c>
       <c r="F45">
-        <v>60.62978707301824</v>
+        <v>62.03978212122797</v>
       </c>
       <c r="G45">
         <v>0.114</v>
@@ -4959,37 +4959,37 @@
         <v>2.311</v>
       </c>
       <c r="M45">
-        <v>14.2965037918177</v>
+        <v>14.62898062418556</v>
       </c>
       <c r="N45">
-        <v>-11.9855037918177</v>
+        <v>-12.31798062418556</v>
       </c>
       <c r="O45">
-        <v>-2.037535644609009</v>
+        <v>-2.094056706111544</v>
       </c>
       <c r="P45">
-        <v>-9.947968147208691</v>
+        <v>-10.22392391807401</v>
       </c>
       <c r="Q45">
-        <v>-9.912968147208691</v>
+        <v>-10.18892391807401</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1182683942189367</v>
+        <v>0.119562472687132</v>
       </c>
       <c r="T45">
-        <v>1.673634970414242</v>
+        <v>1.703521309171639</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02748014519639765</v>
+        <v>0.02685559644193407</v>
       </c>
       <c r="W45">
-        <v>0.2293201817626895</v>
+        <v>0.229467450358992</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1616479129199861</v>
+        <v>0.1579740967172593</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1679206628627504</v>
+        <v>0.1698206628627504</v>
       </c>
       <c r="C46">
-        <v>-13.74213835800555</v>
+        <v>-15.89030816707297</v>
       </c>
       <c r="D46">
-        <v>48.18364376322242</v>
+        <v>47.44546900236473</v>
       </c>
       <c r="E46">
-        <v>61.04027730025533</v>
+        <v>62.45027234846506</v>
       </c>
       <c r="F46">
-        <v>62.03978212122797</v>
+        <v>63.4497771694377</v>
       </c>
       <c r="G46">
         <v>0.114</v>
@@ -5041,37 +5041,37 @@
         <v>2.311</v>
       </c>
       <c r="M46">
-        <v>14.62898062418556</v>
+        <v>14.96145745655341</v>
       </c>
       <c r="N46">
-        <v>-12.31798062418556</v>
+        <v>-12.65045745655341</v>
       </c>
       <c r="O46">
-        <v>-2.094056706111544</v>
+        <v>-2.15057776761408</v>
       </c>
       <c r="P46">
-        <v>-10.22392391807401</v>
+        <v>-10.49987968893933</v>
       </c>
       <c r="Q46">
-        <v>-10.18892391807401</v>
+        <v>-10.46487968893933</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.119562472687132</v>
+        <v>0.1209036085541707</v>
       </c>
       <c r="T46">
-        <v>1.703521309171639</v>
+        <v>1.734494423883851</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02685559644193407</v>
+        <v>0.02625880540989109</v>
       </c>
       <c r="W46">
-        <v>0.229467450358992</v>
+        <v>0.2296081736843477</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1579740967172593</v>
+        <v>0.1544635612346534</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1698206628627504</v>
+        <v>0.1717206628627504</v>
       </c>
       <c r="C47">
-        <v>-15.89030816707297</v>
+        <v>-18.0162015361385</v>
       </c>
       <c r="D47">
-        <v>47.44546900236473</v>
+        <v>46.72957068150892</v>
       </c>
       <c r="E47">
-        <v>62.45027234846506</v>
+        <v>63.86026739667479</v>
       </c>
       <c r="F47">
-        <v>63.4497771694377</v>
+        <v>64.85977221764742</v>
       </c>
       <c r="G47">
         <v>0.114</v>
@@ -5123,37 +5123,37 @@
         <v>2.311</v>
       </c>
       <c r="M47">
-        <v>14.96145745655341</v>
+        <v>15.29393428892126</v>
       </c>
       <c r="N47">
-        <v>-12.65045745655341</v>
+        <v>-12.98293428892126</v>
       </c>
       <c r="O47">
-        <v>-2.15057776761408</v>
+        <v>-2.207098829116615</v>
       </c>
       <c r="P47">
-        <v>-10.49987968893933</v>
+        <v>-10.77583545980465</v>
       </c>
       <c r="Q47">
-        <v>-10.46487968893933</v>
+        <v>-10.74083545980465</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1209036085541707</v>
+        <v>0.1222944161199887</v>
       </c>
       <c r="T47">
-        <v>1.734494423883851</v>
+        <v>1.766614690992811</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02625880540989109</v>
+        <v>0.02568796181402389</v>
       </c>
       <c r="W47">
-        <v>0.2296081736843477</v>
+        <v>0.2297427786042532</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1544635612346534</v>
+        <v>0.1511056577295523</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1717206628627504</v>
+        <v>0.1736206628627504</v>
       </c>
       <c r="C48">
-        <v>-18.0162015361385</v>
+        <v>-20.12081185473063</v>
       </c>
       <c r="D48">
-        <v>46.72957068150892</v>
+        <v>46.03495541112652</v>
       </c>
       <c r="E48">
-        <v>63.86026739667479</v>
+        <v>65.27026244488452</v>
       </c>
       <c r="F48">
-        <v>64.85977221764742</v>
+        <v>66.26976726585715</v>
       </c>
       <c r="G48">
         <v>0.114</v>
@@ -5205,37 +5205,37 @@
         <v>2.311</v>
       </c>
       <c r="M48">
-        <v>15.29393428892126</v>
+        <v>15.62641112128912</v>
       </c>
       <c r="N48">
-        <v>-12.98293428892126</v>
+        <v>-13.31541112128912</v>
       </c>
       <c r="O48">
-        <v>-2.207098829116615</v>
+        <v>-2.26361989061915</v>
       </c>
       <c r="P48">
-        <v>-10.77583545980465</v>
+        <v>-11.05179123066997</v>
       </c>
       <c r="Q48">
-        <v>-10.74083545980465</v>
+        <v>-11.01679123066997</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1222944161199887</v>
+        <v>0.1237377069901772</v>
       </c>
       <c r="T48">
-        <v>1.766614690992811</v>
+        <v>1.799947043653053</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02568796181402389</v>
+        <v>0.0251414094350021</v>
       </c>
       <c r="W48">
-        <v>0.2297427786042532</v>
+        <v>0.2298716556552265</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1511056577295523</v>
+        <v>0.1478906437353065</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1736206628627504</v>
+        <v>0.1755206628627504</v>
       </c>
       <c r="C49">
-        <v>-20.12081185473063</v>
+        <v>-22.20507431224031</v>
       </c>
       <c r="D49">
-        <v>46.03495541112652</v>
+        <v>45.36068800182657</v>
       </c>
       <c r="E49">
-        <v>65.27026244488452</v>
+        <v>66.68025749309425</v>
       </c>
       <c r="F49">
-        <v>66.26976726585715</v>
+        <v>67.67976231406688</v>
       </c>
       <c r="G49">
         <v>0.114</v>
@@ -5287,37 +5287,37 @@
         <v>2.311</v>
       </c>
       <c r="M49">
-        <v>15.62641112128912</v>
+        <v>15.95888795365697</v>
       </c>
       <c r="N49">
-        <v>-13.31541112128912</v>
+        <v>-13.64788795365697</v>
       </c>
       <c r="O49">
-        <v>-2.26361989061915</v>
+        <v>-2.320140952121685</v>
       </c>
       <c r="P49">
-        <v>-11.05179123066997</v>
+        <v>-11.32774700153529</v>
       </c>
       <c r="Q49">
-        <v>-11.01679123066997</v>
+        <v>-11.29274700153529</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1237377069901772</v>
+        <v>0.1252365090476806</v>
       </c>
       <c r="T49">
-        <v>1.799947043653053</v>
+        <v>1.83456140987715</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0251414094350021</v>
+        <v>0.02461763007177289</v>
       </c>
       <c r="W49">
-        <v>0.2298716556552265</v>
+        <v>0.229995162829076</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1478906437353065</v>
+        <v>0.1448095886574876</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1755206628627504</v>
+        <v>0.1774206628627504</v>
       </c>
       <c r="C50">
-        <v>-22.2050743122403</v>
+        <v>-24.26987009863915</v>
       </c>
       <c r="D50">
-        <v>45.36068800182657</v>
+        <v>44.70588726363745</v>
       </c>
       <c r="E50">
-        <v>66.68025749309423</v>
+        <v>68.09025254130397</v>
       </c>
       <c r="F50">
-        <v>67.67976231406686</v>
+        <v>69.0897573622766</v>
       </c>
       <c r="G50">
         <v>0.114</v>
@@ -5369,37 +5369,37 @@
         <v>2.311</v>
       </c>
       <c r="M50">
-        <v>15.95888795365697</v>
+        <v>16.29136478602482</v>
       </c>
       <c r="N50">
-        <v>-13.64788795365697</v>
+        <v>-13.98036478602482</v>
       </c>
       <c r="O50">
-        <v>-2.320140952121684</v>
+        <v>-2.37666201362422</v>
       </c>
       <c r="P50">
-        <v>-11.32774700153528</v>
+        <v>-11.6037027724006</v>
       </c>
       <c r="Q50">
-        <v>-11.29274700153528</v>
+        <v>-11.5687027724006</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1252365090476806</v>
+        <v>0.1267940876564586</v>
       </c>
       <c r="T50">
-        <v>1.83456140987715</v>
+        <v>1.870533202227682</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0246176300717729</v>
+        <v>0.02411522945806325</v>
       </c>
       <c r="W50">
-        <v>0.229995162829076</v>
+        <v>0.2301136288937887</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1448095886574876</v>
+        <v>0.1418542909297837</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1774206628627504</v>
+        <v>0.1793206628627504</v>
       </c>
       <c r="C51">
-        <v>-24.26987009863915</v>
+        <v>-26.31603024654004</v>
       </c>
       <c r="D51">
-        <v>44.70588726363745</v>
+        <v>44.06972216394629</v>
       </c>
       <c r="E51">
-        <v>68.09025254130397</v>
+        <v>69.50024758951369</v>
       </c>
       <c r="F51">
-        <v>69.0897573622766</v>
+        <v>70.49975241048632</v>
       </c>
       <c r="G51">
         <v>0.114</v>
@@ -5451,37 +5451,37 @@
         <v>2.311</v>
       </c>
       <c r="M51">
-        <v>16.29136478602482</v>
+        <v>16.62384161839267</v>
       </c>
       <c r="N51">
-        <v>-13.98036478602482</v>
+        <v>-14.31284161839267</v>
       </c>
       <c r="O51">
-        <v>-2.37666201362422</v>
+        <v>-2.433183075126755</v>
       </c>
       <c r="P51">
-        <v>-11.6037027724006</v>
+        <v>-11.87965854326592</v>
       </c>
       <c r="Q51">
-        <v>-11.5687027724006</v>
+        <v>-11.84465854326592</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1267940876564586</v>
+        <v>0.1284139694095878</v>
       </c>
       <c r="T51">
-        <v>1.870533202227682</v>
+        <v>1.907943866272236</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02411522945806325</v>
+        <v>0.02363292486890198</v>
       </c>
       <c r="W51">
-        <v>0.2301136288937887</v>
+        <v>0.2302273563159129</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1418542909297837</v>
+        <v>0.1390172051111881</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1793206628627504</v>
+        <v>0.1812206628627504</v>
       </c>
       <c r="C52">
-        <v>-26.31603024654004</v>
+        <v>-28.3443391498249</v>
       </c>
       <c r="D52">
-        <v>44.06972216394629</v>
+        <v>43.45140830887115</v>
       </c>
       <c r="E52">
-        <v>69.50024758951369</v>
+        <v>70.91024263772341</v>
       </c>
       <c r="F52">
-        <v>70.49975241048632</v>
+        <v>71.90974745869605</v>
       </c>
       <c r="G52">
         <v>0.114</v>
@@ -5533,37 +5533,37 @@
         <v>2.311</v>
       </c>
       <c r="M52">
-        <v>16.62384161839267</v>
+        <v>16.95631845076053</v>
       </c>
       <c r="N52">
-        <v>-14.31284161839267</v>
+        <v>-14.64531845076053</v>
       </c>
       <c r="O52">
-        <v>-2.433183075126755</v>
+        <v>-2.48970413662929</v>
       </c>
       <c r="P52">
-        <v>-11.87965854326592</v>
+        <v>-12.15561431413124</v>
       </c>
       <c r="Q52">
-        <v>-11.84465854326592</v>
+        <v>-12.12061431413124</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1284139694095878</v>
+        <v>0.1300999687852937</v>
       </c>
       <c r="T52">
-        <v>1.907943866272236</v>
+        <v>1.946881496196159</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02363292486890198</v>
+        <v>0.02316953418519802</v>
       </c>
       <c r="W52">
-        <v>0.2302273563159129</v>
+        <v>0.2303366238391303</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1390172051111881</v>
+        <v>0.1362913775599883</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1812206628627504</v>
+        <v>0.1831206628627504</v>
       </c>
       <c r="C53">
-        <v>-28.3443391498249</v>
+        <v>-30.35553779016534</v>
       </c>
       <c r="D53">
-        <v>43.45140830887115</v>
+        <v>42.85020471674045</v>
       </c>
       <c r="E53">
-        <v>70.91024263772341</v>
+        <v>72.32023768593315</v>
       </c>
       <c r="F53">
-        <v>71.90974745869605</v>
+        <v>73.31974250690578</v>
       </c>
       <c r="G53">
         <v>0.114</v>
@@ -5615,37 +5615,37 @@
         <v>2.311</v>
       </c>
       <c r="M53">
-        <v>16.95631845076053</v>
+        <v>17.28879528312838</v>
       </c>
       <c r="N53">
-        <v>-14.64531845076053</v>
+        <v>-14.97779528312838</v>
       </c>
       <c r="O53">
-        <v>-2.48970413662929</v>
+        <v>-2.546225198131825</v>
       </c>
       <c r="P53">
-        <v>-12.15561431413124</v>
+        <v>-12.43157008499656</v>
       </c>
       <c r="Q53">
-        <v>-12.12061431413124</v>
+        <v>-12.39657008499656</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1300999687852937</v>
+        <v>0.1318562181349873</v>
       </c>
       <c r="T53">
-        <v>1.946881496196159</v>
+        <v>1.987441527366912</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02316953418519802</v>
+        <v>0.02272396622009806</v>
       </c>
       <c r="W53">
-        <v>0.2303366238391303</v>
+        <v>0.2304416887653009</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1362913775599883</v>
+        <v>0.1336703895299886</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1831206628627504</v>
+        <v>0.1850206628627504</v>
       </c>
       <c r="C54">
-        <v>-30.35553779016534</v>
+        <v>-32.35032669934144</v>
       </c>
       <c r="D54">
-        <v>42.85020471674045</v>
+        <v>42.26541085577406</v>
       </c>
       <c r="E54">
-        <v>72.32023768593315</v>
+        <v>73.73023273414287</v>
       </c>
       <c r="F54">
-        <v>73.31974250690578</v>
+        <v>74.72973755511551</v>
       </c>
       <c r="G54">
         <v>0.114</v>
@@ -5697,37 +5697,37 @@
         <v>2.311</v>
       </c>
       <c r="M54">
-        <v>17.28879528312838</v>
+        <v>17.62127211549624</v>
       </c>
       <c r="N54">
-        <v>-14.97779528312838</v>
+        <v>-15.31027211549624</v>
       </c>
       <c r="O54">
-        <v>-2.546225198131825</v>
+        <v>-2.60274625963436</v>
       </c>
       <c r="P54">
-        <v>-12.43157008499656</v>
+        <v>-12.70752585586188</v>
       </c>
       <c r="Q54">
-        <v>-12.39657008499656</v>
+        <v>-12.67252585586188</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1318562181349873</v>
+        <v>0.1336872014995615</v>
       </c>
       <c r="T54">
-        <v>1.987441527366912</v>
+        <v>2.029727517310889</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02272396622009806</v>
+        <v>0.02229521214047357</v>
       </c>
       <c r="W54">
-        <v>0.2304416887653009</v>
+        <v>0.2305427889772763</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1336703895299886</v>
+        <v>0.1311483067086681</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1850206628627504</v>
+        <v>0.1869206628627504</v>
       </c>
       <c r="C55">
-        <v>-32.35032669934144</v>
+        <v>-34.32936868225891</v>
       </c>
       <c r="D55">
-        <v>42.26541085577406</v>
+        <v>41.69636392106632</v>
       </c>
       <c r="E55">
-        <v>73.73023273414287</v>
+        <v>75.1402277823526</v>
       </c>
       <c r="F55">
-        <v>74.72973755511551</v>
+        <v>76.13973260332523</v>
       </c>
       <c r="G55">
         <v>0.114</v>
@@ -5779,37 +5779,37 @@
         <v>2.311</v>
       </c>
       <c r="M55">
-        <v>17.62127211549624</v>
+        <v>17.95374894786409</v>
       </c>
       <c r="N55">
-        <v>-15.31027211549624</v>
+        <v>-15.64274894786409</v>
       </c>
       <c r="O55">
-        <v>-2.60274625963436</v>
+        <v>-2.659267321136895</v>
       </c>
       <c r="P55">
-        <v>-12.70752585586188</v>
+        <v>-12.98348162672719</v>
       </c>
       <c r="Q55">
-        <v>-12.67252585586188</v>
+        <v>-12.94848162672719</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1336872014995615</v>
+        <v>0.1355977928365085</v>
       </c>
       <c r="T55">
-        <v>2.029727517310889</v>
+        <v>2.073852028556778</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02229521214047357</v>
+        <v>0.02188233784157591</v>
       </c>
       <c r="W55">
-        <v>0.2305427889772763</v>
+        <v>0.2306401447369564</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1311483067086681</v>
+        <v>0.1287196343622112</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1869206628627504</v>
+        <v>0.1888206628627504</v>
       </c>
       <c r="C56">
-        <v>-34.32936868225891</v>
+        <v>-36.29329132291766</v>
       </c>
       <c r="D56">
-        <v>41.69636392106632</v>
+        <v>41.14243632861731</v>
       </c>
       <c r="E56">
-        <v>75.1402277823526</v>
+        <v>76.55022283056233</v>
       </c>
       <c r="F56">
-        <v>76.13973260332523</v>
+        <v>77.54972765153497</v>
       </c>
       <c r="G56">
         <v>0.114</v>
@@ -5861,37 +5861,37 @@
         <v>2.311</v>
       </c>
       <c r="M56">
-        <v>17.95374894786409</v>
+        <v>18.28622578023194</v>
       </c>
       <c r="N56">
-        <v>-15.64274894786409</v>
+        <v>-15.97522578023194</v>
       </c>
       <c r="O56">
-        <v>-2.659267321136895</v>
+        <v>-2.715788382639431</v>
       </c>
       <c r="P56">
-        <v>-12.98348162672719</v>
+        <v>-13.25943739759251</v>
       </c>
       <c r="Q56">
-        <v>-12.94848162672719</v>
+        <v>-13.22443739759251</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1355977928365085</v>
+        <v>0.1375932993439865</v>
       </c>
       <c r="T56">
-        <v>2.073852028556778</v>
+        <v>2.119937629191373</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02188233784157591</v>
+        <v>0.02148447715354725</v>
       </c>
       <c r="W56">
-        <v>0.2306401447369564</v>
+        <v>0.2307339602871936</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1287196343622112</v>
+        <v>0.1263792773738074</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1888206628627504</v>
+        <v>0.1907206628627504</v>
       </c>
       <c r="C57">
-        <v>-36.29329132291766</v>
+        <v>-38.24268929325178</v>
       </c>
       <c r="D57">
-        <v>41.14243632861731</v>
+        <v>40.60303340649291</v>
       </c>
       <c r="E57">
-        <v>76.55022283056233</v>
+        <v>77.96021787877206</v>
       </c>
       <c r="F57">
-        <v>77.54972765153497</v>
+        <v>78.95972269974469</v>
       </c>
       <c r="G57">
         <v>0.114</v>
@@ -5943,37 +5943,37 @@
         <v>2.311</v>
       </c>
       <c r="M57">
-        <v>18.28622578023194</v>
+        <v>18.6187026125998</v>
       </c>
       <c r="N57">
-        <v>-15.97522578023194</v>
+        <v>-16.3077026125998</v>
       </c>
       <c r="O57">
-        <v>-2.715788382639431</v>
+        <v>-2.772309444141966</v>
       </c>
       <c r="P57">
-        <v>-13.25943739759251</v>
+        <v>-13.53539316845783</v>
       </c>
       <c r="Q57">
-        <v>-13.22443739759251</v>
+        <v>-13.50039316845783</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1375932993439865</v>
+        <v>0.1396795106927134</v>
       </c>
       <c r="T57">
-        <v>2.119937629191373</v>
+        <v>2.168118029854814</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02148447715354725</v>
+        <v>0.02110082577580534</v>
       </c>
       <c r="W57">
-        <v>0.2307339602871936</v>
+        <v>0.2308244252820651</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1263792773738074</v>
+        <v>0.1241225045635608</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1907206628627504</v>
+        <v>0.1926206628627504</v>
       </c>
       <c r="C58">
-        <v>-38.24268929325178</v>
+        <v>-40.17812648269781</v>
       </c>
       <c r="D58">
-        <v>40.60303340649291</v>
+        <v>40.07759126525661</v>
       </c>
       <c r="E58">
-        <v>77.96021787877206</v>
+        <v>79.37021292698178</v>
       </c>
       <c r="F58">
-        <v>78.95972269974469</v>
+        <v>80.36971774795441</v>
       </c>
       <c r="G58">
         <v>0.114</v>
@@ -6025,37 +6025,37 @@
         <v>2.311</v>
       </c>
       <c r="M58">
-        <v>18.6187026125998</v>
+        <v>18.95117944496765</v>
       </c>
       <c r="N58">
-        <v>-16.3077026125998</v>
+        <v>-16.64017944496765</v>
       </c>
       <c r="O58">
-        <v>-2.772309444141966</v>
+        <v>-2.828830505644501</v>
       </c>
       <c r="P58">
-        <v>-13.53539316845783</v>
+        <v>-13.81134893932315</v>
       </c>
       <c r="Q58">
-        <v>-13.50039316845783</v>
+        <v>-13.77634893932315</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1396795106927134</v>
+        <v>0.1418627551274277</v>
       </c>
       <c r="T58">
-        <v>2.168118029854814</v>
+        <v>2.218539379386321</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02110082577580534</v>
+        <v>0.02073063584991402</v>
       </c>
       <c r="W58">
-        <v>0.2308244252820651</v>
+        <v>0.2309117160665903</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1241225045635608</v>
+        <v>0.1219449167642001</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1926206628627504</v>
+        <v>0.1945206628627504</v>
       </c>
       <c r="C59">
-        <v>-40.17812648269781</v>
+        <v>-42.1001379645235</v>
       </c>
       <c r="D59">
-        <v>40.07759126525661</v>
+        <v>39.56557483164065</v>
       </c>
       <c r="E59">
-        <v>79.37021292698178</v>
+        <v>80.78020797519152</v>
       </c>
       <c r="F59">
-        <v>80.36971774795441</v>
+        <v>81.77971279616415</v>
       </c>
       <c r="G59">
         <v>0.114</v>
@@ -6107,37 +6107,37 @@
         <v>2.311</v>
       </c>
       <c r="M59">
-        <v>18.95117944496765</v>
+        <v>19.28365627733551</v>
       </c>
       <c r="N59">
-        <v>-16.64017944496765</v>
+        <v>-16.97265627733551</v>
       </c>
       <c r="O59">
-        <v>-2.828830505644501</v>
+        <v>-2.885351567147036</v>
       </c>
       <c r="P59">
-        <v>-13.81134893932315</v>
+        <v>-14.08730471018847</v>
       </c>
       <c r="Q59">
-        <v>-13.77634893932315</v>
+        <v>-14.05230471018847</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1418627551274277</v>
+        <v>0.1441499635828427</v>
       </c>
       <c r="T59">
-        <v>2.218539379386321</v>
+        <v>2.271361745562186</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02073063584991402</v>
+        <v>0.02037321109388102</v>
       </c>
       <c r="W59">
-        <v>0.2309117160665903</v>
+        <v>0.2309959968240629</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1219449167642001</v>
+        <v>0.1198424181993001</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1945206628627504</v>
+        <v>0.1964206628627504</v>
       </c>
       <c r="C60">
-        <v>-42.10013796452349</v>
+        <v>-44.0092318133315</v>
       </c>
       <c r="D60">
-        <v>39.56557483164065</v>
+        <v>39.06647603104236</v>
       </c>
       <c r="E60">
-        <v>80.7802079751915</v>
+        <v>82.19020302340122</v>
       </c>
       <c r="F60">
-        <v>81.77971279616413</v>
+        <v>83.18970784437386</v>
       </c>
       <c r="G60">
         <v>0.114</v>
@@ -6189,37 +6189,37 @@
         <v>2.311</v>
       </c>
       <c r="M60">
-        <v>19.2836562773355</v>
+        <v>19.61613310970336</v>
       </c>
       <c r="N60">
-        <v>-16.9726562773355</v>
+        <v>-17.30513310970336</v>
       </c>
       <c r="O60">
-        <v>-2.885351567147036</v>
+        <v>-2.941872628649571</v>
       </c>
       <c r="P60">
-        <v>-14.08730471018847</v>
+        <v>-14.36326048105379</v>
       </c>
       <c r="Q60">
-        <v>-14.05230471018847</v>
+        <v>-14.32826048105379</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1441499635828426</v>
+        <v>0.1465487431824242</v>
       </c>
       <c r="T60">
-        <v>2.271361745562185</v>
+        <v>2.326760812527117</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02037321109388102</v>
+        <v>0.02002790243127287</v>
       </c>
       <c r="W60">
-        <v>0.2309959968240629</v>
+        <v>0.2310774206067059</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1198424181993001</v>
+        <v>0.1178111907721934</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1964206628627504</v>
+        <v>0.1983206628627504</v>
       </c>
       <c r="C61">
-        <v>-44.0092318133315</v>
+        <v>-45.90589078671557</v>
       </c>
       <c r="D61">
-        <v>39.06647603104236</v>
+        <v>38.57981210586802</v>
       </c>
       <c r="E61">
-        <v>82.19020302340122</v>
+        <v>83.60019807161095</v>
       </c>
       <c r="F61">
-        <v>83.18970784437386</v>
+        <v>84.59970289258358</v>
       </c>
       <c r="G61">
         <v>0.114</v>
@@ -6271,37 +6271,37 @@
         <v>2.311</v>
       </c>
       <c r="M61">
-        <v>19.61613310970336</v>
+        <v>19.94860994207121</v>
       </c>
       <c r="N61">
-        <v>-17.30513310970336</v>
+        <v>-17.63760994207121</v>
       </c>
       <c r="O61">
-        <v>-2.941872628649571</v>
+        <v>-2.998393690152106</v>
       </c>
       <c r="P61">
-        <v>-14.36326048105379</v>
+        <v>-14.6392162519191</v>
       </c>
       <c r="Q61">
-        <v>-14.32826048105379</v>
+        <v>-14.6042162519191</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1465487431824242</v>
+        <v>0.1490674617619848</v>
       </c>
       <c r="T61">
-        <v>2.326760812527117</v>
+        <v>2.384929832840295</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02002790243127287</v>
+        <v>0.01969410405741832</v>
       </c>
       <c r="W61">
-        <v>0.2310774206067059</v>
+        <v>0.2311561302632608</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1178111907721934</v>
+        <v>0.1158476709259901</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1983206628627504</v>
+        <v>0.2002206628627504</v>
       </c>
       <c r="C62">
-        <v>-45.90589078671557</v>
+        <v>-47.79057388276965</v>
       </c>
       <c r="D62">
-        <v>38.57981210586802</v>
+        <v>38.10512405802367</v>
       </c>
       <c r="E62">
-        <v>83.60019807161095</v>
+        <v>85.01019311982068</v>
       </c>
       <c r="F62">
-        <v>84.59970289258358</v>
+        <v>86.00969794079332</v>
       </c>
       <c r="G62">
         <v>0.114</v>
@@ -6353,37 +6353,37 @@
         <v>2.311</v>
       </c>
       <c r="M62">
-        <v>19.94860994207121</v>
+        <v>20.28108677443906</v>
       </c>
       <c r="N62">
-        <v>-17.63760994207121</v>
+        <v>-17.97008677443906</v>
       </c>
       <c r="O62">
-        <v>-2.998393690152106</v>
+        <v>-3.054914751654641</v>
       </c>
       <c r="P62">
-        <v>-14.6392162519191</v>
+        <v>-14.91517202278442</v>
       </c>
       <c r="Q62">
-        <v>-14.6042162519191</v>
+        <v>-14.88017202278442</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1490674617619848</v>
+        <v>0.1517153453969075</v>
       </c>
       <c r="T62">
-        <v>2.384929832840295</v>
+        <v>2.446081879836199</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01969410405741832</v>
+        <v>0.01937124989254261</v>
       </c>
       <c r="W62">
-        <v>0.2311561302632608</v>
+        <v>0.2312322592753385</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1158476709259901</v>
+        <v>0.1139485287796624</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2002206628627504</v>
+        <v>0.2021206628627504</v>
       </c>
       <c r="C63">
-        <v>-47.79057388276965</v>
+        <v>-49.66371778401241</v>
       </c>
       <c r="D63">
-        <v>38.10512405802367</v>
+        <v>37.64197520499064</v>
       </c>
       <c r="E63">
-        <v>85.01019311982068</v>
+        <v>86.42018816803041</v>
       </c>
       <c r="F63">
-        <v>86.00969794079332</v>
+        <v>87.41969298900304</v>
       </c>
       <c r="G63">
         <v>0.114</v>
@@ -6435,37 +6435,37 @@
         <v>2.311</v>
       </c>
       <c r="M63">
-        <v>20.28108677443906</v>
+        <v>20.61356360680692</v>
       </c>
       <c r="N63">
-        <v>-17.97008677443906</v>
+        <v>-18.30256360680692</v>
       </c>
       <c r="O63">
-        <v>-3.054914751654641</v>
+        <v>-3.111435813157176</v>
       </c>
       <c r="P63">
-        <v>-14.91517202278442</v>
+        <v>-15.19112779364974</v>
       </c>
       <c r="Q63">
-        <v>-14.88017202278442</v>
+        <v>-15.15612779364974</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1517153453969075</v>
+        <v>0.154502591328405</v>
       </c>
       <c r="T63">
-        <v>2.446081879836199</v>
+        <v>2.510452455621363</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01937124989254261</v>
+        <v>0.01905881037814676</v>
       </c>
       <c r="W63">
-        <v>0.2312322592753385</v>
+        <v>0.231305932512833</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1139485287796624</v>
+        <v>0.1121106492832162</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2021206628627504</v>
+        <v>0.2040206628627504</v>
       </c>
       <c r="C64">
-        <v>-49.66371778401241</v>
+        <v>-51.52573819727526</v>
       </c>
       <c r="D64">
-        <v>37.64197520499064</v>
+        <v>37.1899498399375</v>
       </c>
       <c r="E64">
-        <v>86.42018816803041</v>
+        <v>87.83018321624013</v>
       </c>
       <c r="F64">
-        <v>87.41969298900304</v>
+        <v>88.82968803721276</v>
       </c>
       <c r="G64">
         <v>0.114</v>
@@ -6517,37 +6517,37 @@
         <v>2.311</v>
       </c>
       <c r="M64">
-        <v>20.61356360680692</v>
+        <v>20.94604043917477</v>
       </c>
       <c r="N64">
-        <v>-18.30256360680692</v>
+        <v>-18.63504043917477</v>
       </c>
       <c r="O64">
-        <v>-3.111435813157176</v>
+        <v>-3.167956874659711</v>
       </c>
       <c r="P64">
-        <v>-15.19112779364974</v>
+        <v>-15.46708356451506</v>
       </c>
       <c r="Q64">
-        <v>-15.15612779364974</v>
+        <v>-15.43208356451506</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.154502591328405</v>
+        <v>0.1574404992021457</v>
       </c>
       <c r="T64">
-        <v>2.510452455621363</v>
+        <v>2.578302521989508</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01905881037814676</v>
+        <v>0.01875628957849364</v>
       </c>
       <c r="W64">
-        <v>0.231305932512833</v>
+        <v>0.2313772669173912</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1121106492832162</v>
+        <v>0.1103311151676096</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2040206628627504</v>
+        <v>0.2059206628627504</v>
       </c>
       <c r="C65">
-        <v>-51.52573819727526</v>
+        <v>-53.37703109819528</v>
       </c>
       <c r="D65">
-        <v>37.1899498399375</v>
+        <v>36.74865198722722</v>
       </c>
       <c r="E65">
-        <v>87.83018321624013</v>
+        <v>89.24017826444987</v>
       </c>
       <c r="F65">
-        <v>88.82968803721276</v>
+        <v>90.2396830854225</v>
       </c>
       <c r="G65">
         <v>0.114</v>
@@ -6599,37 +6599,37 @@
         <v>2.311</v>
       </c>
       <c r="M65">
-        <v>20.94604043917477</v>
+        <v>21.27851727154263</v>
       </c>
       <c r="N65">
-        <v>-18.63504043917477</v>
+        <v>-18.96751727154263</v>
       </c>
       <c r="O65">
-        <v>-3.167956874659711</v>
+        <v>-3.224477936162247</v>
       </c>
       <c r="P65">
-        <v>-15.46708356451506</v>
+        <v>-15.74303933538038</v>
       </c>
       <c r="Q65">
-        <v>-15.43208356451506</v>
+        <v>-15.70803933538038</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1574404992021457</v>
+        <v>0.1605416241799831</v>
       </c>
       <c r="T65">
-        <v>2.578302521989508</v>
+        <v>2.649922036489217</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01875628957849364</v>
+        <v>0.01846322255382967</v>
       </c>
       <c r="W65">
-        <v>0.2313772669173912</v>
+        <v>0.231446372121807</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1103311151676096</v>
+        <v>0.1086071914931157</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2059206628627504</v>
+        <v>0.2078206628627504</v>
       </c>
       <c r="C66">
-        <v>-53.37703109819528</v>
+        <v>-55.21797388814385</v>
       </c>
       <c r="D66">
-        <v>36.74865198722722</v>
+        <v>36.31770424548838</v>
       </c>
       <c r="E66">
-        <v>89.24017826444987</v>
+        <v>90.65017331265959</v>
       </c>
       <c r="F66">
-        <v>90.2396830854225</v>
+        <v>91.64967813363222</v>
       </c>
       <c r="G66">
         <v>0.114</v>
@@ -6681,37 +6681,37 @@
         <v>2.311</v>
       </c>
       <c r="M66">
-        <v>21.27851727154263</v>
+        <v>21.61099410391048</v>
       </c>
       <c r="N66">
-        <v>-18.96751727154263</v>
+        <v>-19.29999410391048</v>
       </c>
       <c r="O66">
-        <v>-3.224477936162247</v>
+        <v>-3.280998997664782</v>
       </c>
       <c r="P66">
-        <v>-15.74303933538038</v>
+        <v>-16.0189951062457</v>
       </c>
       <c r="Q66">
-        <v>-15.70803933538038</v>
+        <v>-15.9839951062457</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1605416241799831</v>
+        <v>0.1638199562994112</v>
       </c>
       <c r="T66">
-        <v>2.649922036489217</v>
+        <v>2.725634094674623</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01846322255382967</v>
+        <v>0.01817917297607845</v>
       </c>
       <c r="W66">
-        <v>0.231446372121807</v>
+        <v>0.2315133510122407</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1086071914931157</v>
+        <v>0.1069363116239909</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2078206628627504</v>
+        <v>0.2097206628627504</v>
       </c>
       <c r="C67">
-        <v>-55.21797388814385</v>
+        <v>-57.04892647069568</v>
       </c>
       <c r="D67">
-        <v>36.31770424548838</v>
+        <v>35.89674671114626</v>
       </c>
       <c r="E67">
-        <v>90.65017331265959</v>
+        <v>92.06016836086931</v>
       </c>
       <c r="F67">
-        <v>91.64967813363222</v>
+        <v>93.05967318184194</v>
       </c>
       <c r="G67">
         <v>0.114</v>
@@ -6763,37 +6763,37 @@
         <v>2.311</v>
       </c>
       <c r="M67">
-        <v>21.61099410391048</v>
+        <v>21.94347093627833</v>
       </c>
       <c r="N67">
-        <v>-19.29999410391048</v>
+        <v>-19.63247093627833</v>
       </c>
       <c r="O67">
-        <v>-3.280998997664782</v>
+        <v>-3.337520059167316</v>
       </c>
       <c r="P67">
-        <v>-16.0189951062457</v>
+        <v>-16.29495087711101</v>
       </c>
       <c r="Q67">
-        <v>-15.9839951062457</v>
+        <v>-16.25995087711101</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1638199562994112</v>
+        <v>0.167291131484688</v>
       </c>
       <c r="T67">
-        <v>2.725634094674623</v>
+        <v>2.805799803341523</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01817917297607845</v>
+        <v>0.01790373096128938</v>
       </c>
       <c r="W67">
-        <v>0.2315133510122407</v>
+        <v>0.231578300239328</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1069363116239909</v>
+        <v>0.1053160644781728</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2097206628627504</v>
+        <v>0.2116206628627504</v>
       </c>
       <c r="C68">
-        <v>-57.04892647069568</v>
+        <v>-58.87023225409185</v>
       </c>
       <c r="D68">
-        <v>35.89674671114626</v>
+        <v>35.48543597595984</v>
       </c>
       <c r="E68">
-        <v>92.06016836086931</v>
+        <v>93.47016340907905</v>
       </c>
       <c r="F68">
-        <v>93.05967318184194</v>
+        <v>94.46966823005168</v>
       </c>
       <c r="G68">
         <v>0.114</v>
@@ -6845,37 +6845,37 @@
         <v>2.311</v>
       </c>
       <c r="M68">
-        <v>21.94347093627833</v>
+        <v>22.27594776864619</v>
       </c>
       <c r="N68">
-        <v>-19.63247093627833</v>
+        <v>-19.96494776864619</v>
       </c>
       <c r="O68">
-        <v>-3.337520059167316</v>
+        <v>-3.394041120669852</v>
       </c>
       <c r="P68">
-        <v>-16.29495087711101</v>
+        <v>-16.57090664797634</v>
       </c>
       <c r="Q68">
-        <v>-16.25995087711101</v>
+        <v>-16.53590664797634</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.167291131484688</v>
+        <v>0.1709726809236179</v>
       </c>
       <c r="T68">
-        <v>2.805799803341523</v>
+        <v>2.890824039806418</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01790373096128938</v>
+        <v>0.01763651109619551</v>
       </c>
       <c r="W68">
-        <v>0.231578300239328</v>
+        <v>0.2316413106835171</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1053160644781728</v>
+        <v>0.1037441829187971</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2116206628627504</v>
+        <v>0.2135206628627504</v>
       </c>
       <c r="C69">
-        <v>-58.87023225409185</v>
+        <v>-60.68221908556501</v>
       </c>
       <c r="D69">
-        <v>35.48543597595984</v>
+        <v>35.0834441926964</v>
       </c>
       <c r="E69">
-        <v>93.47016340907905</v>
+        <v>94.88015845728877</v>
       </c>
       <c r="F69">
-        <v>94.46966823005168</v>
+        <v>95.8796632782614</v>
       </c>
       <c r="G69">
         <v>0.114</v>
@@ -6927,37 +6927,37 @@
         <v>2.311</v>
       </c>
       <c r="M69">
-        <v>22.27594776864619</v>
+        <v>22.60842460101404</v>
       </c>
       <c r="N69">
-        <v>-19.96494776864619</v>
+        <v>-20.29742460101404</v>
       </c>
       <c r="O69">
-        <v>-3.394041120669852</v>
+        <v>-3.450562182172387</v>
       </c>
       <c r="P69">
-        <v>-16.57090664797634</v>
+        <v>-16.84686241884165</v>
       </c>
       <c r="Q69">
-        <v>-16.53590664797634</v>
+        <v>-16.81186241884165</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1709726809236179</v>
+        <v>0.174884327202481</v>
       </c>
       <c r="T69">
-        <v>2.890824039806418</v>
+        <v>2.981162291050369</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01763651109619551</v>
+        <v>0.01737715063889851</v>
       </c>
       <c r="W69">
-        <v>0.2316413106835171</v>
+        <v>0.2317024678793477</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1037441829187971</v>
+        <v>0.1022185331699913</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2135206628627504</v>
+        <v>0.2154206628627504</v>
       </c>
       <c r="C70">
-        <v>-60.68221908556501</v>
+        <v>-62.48520012287008</v>
       </c>
       <c r="D70">
-        <v>35.0834441926964</v>
+        <v>34.69045820360106</v>
       </c>
       <c r="E70">
-        <v>94.88015845728877</v>
+        <v>96.29015350549851</v>
       </c>
       <c r="F70">
-        <v>95.8796632782614</v>
+        <v>97.28965832647114</v>
       </c>
       <c r="G70">
         <v>0.114</v>
@@ -7009,37 +7009,37 @@
         <v>2.311</v>
       </c>
       <c r="M70">
-        <v>22.60842460101404</v>
+        <v>22.9409014333819</v>
       </c>
       <c r="N70">
-        <v>-20.29742460101404</v>
+        <v>-20.6299014333819</v>
       </c>
       <c r="O70">
-        <v>-3.450562182172387</v>
+        <v>-3.507083243674923</v>
       </c>
       <c r="P70">
-        <v>-16.84686241884165</v>
+        <v>-17.12281818970697</v>
       </c>
       <c r="Q70">
-        <v>-16.81186241884165</v>
+        <v>-17.08781818970697</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.174884327202481</v>
+        <v>0.1790483377573998</v>
       </c>
       <c r="T70">
-        <v>2.981162291050369</v>
+        <v>3.077328816568123</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01737715063889851</v>
+        <v>0.01712530787601593</v>
       </c>
       <c r="W70">
-        <v>0.2317024678793477</v>
+        <v>0.2317618524028354</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1022185331699913</v>
+        <v>0.1007371051530348</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2154206628627504</v>
+        <v>0.2173206628627504</v>
       </c>
       <c r="C71">
-        <v>-62.48520012287008</v>
+        <v>-64.27947464788886</v>
       </c>
       <c r="D71">
-        <v>34.69045820360106</v>
+        <v>34.30617872679201</v>
       </c>
       <c r="E71">
-        <v>96.29015350549851</v>
+        <v>97.70014855370823</v>
       </c>
       <c r="F71">
-        <v>97.28965832647114</v>
+        <v>98.69965337468086</v>
       </c>
       <c r="G71">
         <v>0.114</v>
@@ -7091,37 +7091,37 @@
         <v>2.311</v>
       </c>
       <c r="M71">
-        <v>22.9409014333819</v>
+        <v>23.27337826574975</v>
       </c>
       <c r="N71">
-        <v>-20.6299014333819</v>
+        <v>-20.96237826574975</v>
       </c>
       <c r="O71">
-        <v>-3.507083243674923</v>
+        <v>-3.563604305177457</v>
       </c>
       <c r="P71">
-        <v>-17.12281818970697</v>
+        <v>-17.39877396057229</v>
       </c>
       <c r="Q71">
-        <v>-17.08781818970697</v>
+        <v>-17.36377396057229</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1790483377573998</v>
+        <v>0.1834899490159797</v>
       </c>
       <c r="T71">
-        <v>3.077328816568123</v>
+        <v>3.17990644378706</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01712530787601593</v>
+        <v>0.01688066062064427</v>
       </c>
       <c r="W71">
-        <v>0.2317618524028354</v>
+        <v>0.2318195402256521</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1007371051530348</v>
+        <v>0.09929800365084862</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2173206628627504</v>
+        <v>0.2192206628627504</v>
       </c>
       <c r="C72">
-        <v>-64.27947464788886</v>
+        <v>-66.06532882675185</v>
       </c>
       <c r="D72">
-        <v>34.30617872679201</v>
+        <v>33.93031959613874</v>
       </c>
       <c r="E72">
-        <v>97.70014855370823</v>
+        <v>99.11014360191795</v>
       </c>
       <c r="F72">
-        <v>98.69965337468086</v>
+        <v>100.1096484228906</v>
       </c>
       <c r="G72">
         <v>0.114</v>
@@ -7173,37 +7173,37 @@
         <v>2.311</v>
       </c>
       <c r="M72">
-        <v>23.27337826574975</v>
+        <v>23.6058550981176</v>
       </c>
       <c r="N72">
-        <v>-20.96237826574975</v>
+        <v>-21.2948550981176</v>
       </c>
       <c r="O72">
-        <v>-3.563604305177457</v>
+        <v>-3.620125366679992</v>
       </c>
       <c r="P72">
-        <v>-17.39877396057229</v>
+        <v>-17.67472973143761</v>
       </c>
       <c r="Q72">
-        <v>-17.36377396057229</v>
+        <v>-17.63972973143761</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1834899490159797</v>
+        <v>0.1882378782923929</v>
       </c>
       <c r="T72">
-        <v>3.17990644378706</v>
+        <v>3.289558390124546</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01688066062064427</v>
+        <v>0.01664290483725491</v>
       </c>
       <c r="W72">
-        <v>0.2318195402256521</v>
+        <v>0.2318756030393753</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.09929800365084862</v>
+        <v>0.09789944021914654</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2192206628627504</v>
+        <v>0.2211206628627504</v>
       </c>
       <c r="C73">
-        <v>-66.06532882675182</v>
+        <v>-67.84303642053374</v>
       </c>
       <c r="D73">
-        <v>33.93031959613875</v>
+        <v>33.56260705056657</v>
       </c>
       <c r="E73">
-        <v>99.11014360191794</v>
+        <v>100.5201386501277</v>
       </c>
       <c r="F73">
-        <v>100.1096484228906</v>
+        <v>101.5196434711003</v>
       </c>
       <c r="G73">
         <v>0.114</v>
@@ -7255,37 +7255,37 @@
         <v>2.311</v>
       </c>
       <c r="M73">
-        <v>23.6058550981176</v>
+        <v>23.93833193048545</v>
       </c>
       <c r="N73">
-        <v>-21.2948550981176</v>
+        <v>-21.62733193048545</v>
       </c>
       <c r="O73">
-        <v>-3.620125366679992</v>
+        <v>-3.676646428182527</v>
       </c>
       <c r="P73">
-        <v>-17.6747297314376</v>
+        <v>-17.95068550230292</v>
       </c>
       <c r="Q73">
-        <v>-17.6397297314376</v>
+        <v>-17.91568550230292</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1882378782923928</v>
+        <v>0.193324945374264</v>
       </c>
       <c r="T73">
-        <v>3.289558390124544</v>
+        <v>3.407042618343278</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01664290483725492</v>
+        <v>0.01641175338118193</v>
       </c>
       <c r="W73">
-        <v>0.2318756030393753</v>
+        <v>0.2319301085527173</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.09789944021914654</v>
+        <v>0.09653972577165837</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2211206628627504</v>
+        <v>0.2230206628627504</v>
       </c>
       <c r="C74">
-        <v>-67.84303642053374</v>
+        <v>-69.61285945023263</v>
       </c>
       <c r="D74">
-        <v>33.56260705056657</v>
+        <v>33.2027790690774</v>
       </c>
       <c r="E74">
-        <v>100.5201386501277</v>
+        <v>101.9301336983374</v>
       </c>
       <c r="F74">
-        <v>101.5196434711003</v>
+        <v>102.92963851931</v>
       </c>
       <c r="G74">
         <v>0.114</v>
@@ -7337,37 +7337,37 @@
         <v>2.311</v>
       </c>
       <c r="M74">
-        <v>23.93833193048545</v>
+        <v>24.27080876285331</v>
       </c>
       <c r="N74">
-        <v>-21.62733193048545</v>
+        <v>-21.95980876285331</v>
       </c>
       <c r="O74">
-        <v>-3.676646428182527</v>
+        <v>-3.733167489685062</v>
       </c>
       <c r="P74">
-        <v>-17.95068550230292</v>
+        <v>-18.22664127316824</v>
       </c>
       <c r="Q74">
-        <v>-17.91568550230292</v>
+        <v>-18.19164127316824</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.193324945374264</v>
+        <v>0.1987888322399775</v>
       </c>
       <c r="T74">
-        <v>3.407042618343278</v>
+        <v>3.533229381985622</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01641175338118193</v>
+        <v>0.01618693484171368</v>
       </c>
       <c r="W74">
-        <v>0.2319301085527173</v>
+        <v>0.2319831207643239</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.09653972577165837</v>
+        <v>0.09521726377478634</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2230206628627504</v>
+        <v>0.2249206628627504</v>
       </c>
       <c r="C75">
-        <v>-69.61285945023263</v>
+        <v>-71.37504881942689</v>
       </c>
       <c r="D75">
-        <v>33.2027790690774</v>
+        <v>32.85058474809286</v>
       </c>
       <c r="E75">
-        <v>101.9301336983374</v>
+        <v>103.3401287465471</v>
       </c>
       <c r="F75">
-        <v>102.92963851931</v>
+        <v>104.3396335675198</v>
       </c>
       <c r="G75">
         <v>0.114</v>
@@ -7419,37 +7419,37 @@
         <v>2.311</v>
       </c>
       <c r="M75">
-        <v>24.27080876285331</v>
+        <v>24.60328559522116</v>
       </c>
       <c r="N75">
-        <v>-21.95980876285331</v>
+        <v>-22.29228559522116</v>
       </c>
       <c r="O75">
-        <v>-3.733167489685062</v>
+        <v>-3.789688551187597</v>
       </c>
       <c r="P75">
-        <v>-18.22664127316824</v>
+        <v>-18.50259704403356</v>
       </c>
       <c r="Q75">
-        <v>-18.19164127316824</v>
+        <v>-18.46759704403356</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1987888322399775</v>
+        <v>0.2046730180953612</v>
       </c>
       <c r="T75">
-        <v>3.533229381985622</v>
+        <v>3.669122819754299</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01618693484171368</v>
+        <v>0.01596819247898783</v>
       </c>
       <c r="W75">
-        <v>0.2319831207643239</v>
+        <v>0.2320347002134547</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.09521726377478634</v>
+        <v>0.09393054399404599</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2249206628627504</v>
+        <v>0.2268206628627504</v>
       </c>
       <c r="C76">
-        <v>-71.37504881942689</v>
+        <v>-73.12984489771958</v>
       </c>
       <c r="D76">
-        <v>32.85058474809286</v>
+        <v>32.50578371800989</v>
       </c>
       <c r="E76">
-        <v>103.3401287465471</v>
+        <v>104.7501237947568</v>
       </c>
       <c r="F76">
-        <v>104.3396335675198</v>
+        <v>105.7496286157295</v>
       </c>
       <c r="G76">
         <v>0.114</v>
@@ -7501,37 +7501,37 @@
         <v>2.311</v>
       </c>
       <c r="M76">
-        <v>24.60328559522116</v>
+        <v>24.93576242758901</v>
       </c>
       <c r="N76">
-        <v>-22.29228559522116</v>
+        <v>-22.62476242758901</v>
       </c>
       <c r="O76">
-        <v>-3.789688551187597</v>
+        <v>-3.846209612690132</v>
       </c>
       <c r="P76">
-        <v>-18.50259704403356</v>
+        <v>-18.77855281489888</v>
       </c>
       <c r="Q76">
-        <v>-18.46759704403356</v>
+        <v>-18.74355281489888</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2046730180953612</v>
+        <v>0.2110279388191756</v>
       </c>
       <c r="T76">
-        <v>3.669122819754299</v>
+        <v>3.815887732544471</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01596819247898783</v>
+        <v>0.01575528324593466</v>
       </c>
       <c r="W76">
-        <v>0.2320347002134547</v>
+        <v>0.2320849042106086</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.09393054399404599</v>
+        <v>0.09267813674079206</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2268206628627504</v>
+        <v>0.2287206628627504</v>
       </c>
       <c r="C77">
-        <v>-73.12984489771958</v>
+        <v>-74.87747806782131</v>
       </c>
       <c r="D77">
-        <v>32.50578371800989</v>
+        <v>32.1681455961179</v>
       </c>
       <c r="E77">
-        <v>104.7501237947568</v>
+        <v>106.1601188429666</v>
       </c>
       <c r="F77">
-        <v>105.7496286157295</v>
+        <v>107.1596236639392</v>
       </c>
       <c r="G77">
         <v>0.114</v>
@@ -7583,37 +7583,37 @@
         <v>2.311</v>
       </c>
       <c r="M77">
-        <v>24.93576242758901</v>
+        <v>25.26823925995687</v>
       </c>
       <c r="N77">
-        <v>-22.62476242758901</v>
+        <v>-22.95723925995687</v>
       </c>
       <c r="O77">
-        <v>-3.846209612690132</v>
+        <v>-3.902730674192668</v>
       </c>
       <c r="P77">
-        <v>-18.77855281489888</v>
+        <v>-19.0545085857642</v>
       </c>
       <c r="Q77">
-        <v>-18.74355281489888</v>
+        <v>-19.0195085857642</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2110279388191756</v>
+        <v>0.2179124362699746</v>
       </c>
       <c r="T77">
-        <v>3.815887732544471</v>
+        <v>3.974883054733824</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01575528324593466</v>
+        <v>0.01554797688743551</v>
       </c>
       <c r="W77">
-        <v>0.2320849042106086</v>
+        <v>0.2321337870499427</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.09267813674079206</v>
+        <v>0.09145868757315012</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2287206628627504</v>
+        <v>0.2306206628627504</v>
       </c>
       <c r="C78">
-        <v>-74.87747806782131</v>
+        <v>-76.61816923888833</v>
       </c>
       <c r="D78">
-        <v>32.1681455961179</v>
+        <v>31.83744947326062</v>
       </c>
       <c r="E78">
-        <v>106.1601188429666</v>
+        <v>107.5701138911763</v>
       </c>
       <c r="F78">
-        <v>107.1596236639392</v>
+        <v>108.5696187121489</v>
       </c>
       <c r="G78">
         <v>0.114</v>
@@ -7665,37 +7665,37 @@
         <v>2.311</v>
       </c>
       <c r="M78">
-        <v>25.26823925995687</v>
+        <v>25.60071609232472</v>
       </c>
       <c r="N78">
-        <v>-22.95723925995687</v>
+        <v>-23.28971609232472</v>
       </c>
       <c r="O78">
-        <v>-3.902730674192668</v>
+        <v>-3.959251735695203</v>
       </c>
       <c r="P78">
-        <v>-19.0545085857642</v>
+        <v>-19.33046435662952</v>
       </c>
       <c r="Q78">
-        <v>-19.0195085857642</v>
+        <v>-19.29546435662952</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2179124362699746</v>
+        <v>0.225395585673017</v>
       </c>
       <c r="T78">
-        <v>3.974883054733824</v>
+        <v>4.147704057113557</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01554797688743551</v>
+        <v>0.01534605510967661</v>
       </c>
       <c r="W78">
-        <v>0.2321337870499427</v>
+        <v>0.2321814002051383</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.09145868757315012</v>
+        <v>0.0902709124098624</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2306206628627504</v>
+        <v>0.2325206628627504</v>
       </c>
       <c r="C79">
-        <v>-76.61816923888833</v>
+        <v>-78.35213032851929</v>
       </c>
       <c r="D79">
-        <v>31.83744947326062</v>
+        <v>31.51348343183938</v>
       </c>
       <c r="E79">
-        <v>107.5701138911763</v>
+        <v>108.980108939386</v>
       </c>
       <c r="F79">
-        <v>108.5696187121489</v>
+        <v>109.9796137603587</v>
       </c>
       <c r="G79">
         <v>0.114</v>
@@ -7747,37 +7747,37 @@
         <v>2.311</v>
       </c>
       <c r="M79">
-        <v>25.60071609232472</v>
+        <v>25.93319292469258</v>
       </c>
       <c r="N79">
-        <v>-23.28971609232472</v>
+        <v>-23.62219292469258</v>
       </c>
       <c r="O79">
-        <v>-3.959251735695203</v>
+        <v>-4.015772797197738</v>
       </c>
       <c r="P79">
-        <v>-19.33046435662952</v>
+        <v>-19.60642012749484</v>
       </c>
       <c r="Q79">
-        <v>-19.29546435662952</v>
+        <v>-19.57142012749484</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.225395585673017</v>
+        <v>0.2335590213854269</v>
       </c>
       <c r="T79">
-        <v>4.147704057113557</v>
+        <v>4.336236059709628</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01534605510967661</v>
+        <v>0.01514931081339871</v>
       </c>
       <c r="W79">
-        <v>0.2321814002051383</v>
+        <v>0.2322277925102006</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.0902709124098624</v>
+        <v>0.08911359301999233</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2325206628627504</v>
+        <v>0.2344206628627504</v>
       </c>
       <c r="C80">
-        <v>-78.35213032851929</v>
+        <v>-80.07956471562088</v>
       </c>
       <c r="D80">
-        <v>31.51348343183938</v>
+        <v>31.19604409294752</v>
       </c>
       <c r="E80">
-        <v>108.980108939386</v>
+        <v>110.3901039875958</v>
       </c>
       <c r="F80">
-        <v>109.9796137603587</v>
+        <v>111.3896088085684</v>
       </c>
       <c r="G80">
         <v>0.114</v>
@@ -7829,37 +7829,37 @@
         <v>2.311</v>
       </c>
       <c r="M80">
-        <v>25.93319292469258</v>
+        <v>26.26566975706043</v>
       </c>
       <c r="N80">
-        <v>-23.62219292469258</v>
+        <v>-23.95466975706043</v>
       </c>
       <c r="O80">
-        <v>-4.015772797197738</v>
+        <v>-4.072293858700274</v>
       </c>
       <c r="P80">
-        <v>-19.60642012749484</v>
+        <v>-19.88237589836016</v>
       </c>
       <c r="Q80">
-        <v>-19.57142012749484</v>
+        <v>-19.84737589836016</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2335590213854269</v>
+        <v>0.2424999271656853</v>
       </c>
       <c r="T80">
-        <v>4.336236059709628</v>
+        <v>4.542723491124372</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01514931081339871</v>
+        <v>0.014957547385381</v>
       </c>
       <c r="W80">
-        <v>0.2322277925102006</v>
+        <v>0.2322730103265272</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.08911359301999233</v>
+        <v>0.08798557285518238</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2344206628627504</v>
+        <v>0.2363206628627504</v>
       </c>
       <c r="C81">
-        <v>-80.07956471562088</v>
+        <v>-81.80066766617557</v>
       </c>
       <c r="D81">
-        <v>31.19604409294752</v>
+        <v>30.88493619060256</v>
       </c>
       <c r="E81">
-        <v>110.3901039875958</v>
+        <v>111.8000990358055</v>
       </c>
       <c r="F81">
-        <v>111.3896088085684</v>
+        <v>112.7996038567781</v>
       </c>
       <c r="G81">
         <v>0.114</v>
@@ -7911,37 +7911,37 @@
         <v>2.311</v>
       </c>
       <c r="M81">
-        <v>26.26566975706043</v>
+        <v>26.59814658942828</v>
       </c>
       <c r="N81">
-        <v>-23.95466975706043</v>
+        <v>-24.28714658942828</v>
       </c>
       <c r="O81">
-        <v>-4.072293858700274</v>
+        <v>-4.128814920202808</v>
       </c>
       <c r="P81">
-        <v>-19.88237589836016</v>
+        <v>-20.15833166922548</v>
       </c>
       <c r="Q81">
-        <v>-19.84737589836016</v>
+        <v>-20.12333166922548</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2424999271656853</v>
+        <v>0.2523349235239696</v>
       </c>
       <c r="T81">
-        <v>4.542723491124372</v>
+        <v>4.76985966568059</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.014957547385381</v>
+        <v>0.01477057804306374</v>
       </c>
       <c r="W81">
-        <v>0.2322730103265272</v>
+        <v>0.2323170976974456</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.08798557285518238</v>
+        <v>0.08688575319449254</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2363206628627504</v>
+        <v>0.2382206628627504</v>
       </c>
       <c r="C82">
-        <v>-81.80066766617557</v>
+        <v>-83.51562673378481</v>
       </c>
       <c r="D82">
-        <v>30.88493619060256</v>
+        <v>30.57997217120304</v>
       </c>
       <c r="E82">
-        <v>111.8000990358055</v>
+        <v>113.2100940840152</v>
       </c>
       <c r="F82">
-        <v>112.7996038567781</v>
+        <v>114.2095989049879</v>
       </c>
       <c r="G82">
         <v>0.114</v>
@@ -7993,37 +7993,37 @@
         <v>2.311</v>
       </c>
       <c r="M82">
-        <v>26.59814658942828</v>
+        <v>26.93062342179614</v>
       </c>
       <c r="N82">
-        <v>-24.28714658942828</v>
+        <v>-24.61962342179614</v>
       </c>
       <c r="O82">
-        <v>-4.128814920202808</v>
+        <v>-4.185335981705344</v>
       </c>
       <c r="P82">
-        <v>-20.15833166922548</v>
+        <v>-20.4342874400908</v>
       </c>
       <c r="Q82">
-        <v>-20.12333166922548</v>
+        <v>-20.3992874400908</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2523349235239696</v>
+        <v>0.2632051826568101</v>
       </c>
       <c r="T82">
-        <v>4.76985966568059</v>
+        <v>5.020904911242726</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01477057804306374</v>
+        <v>0.01458822522771727</v>
       </c>
       <c r="W82">
-        <v>0.2323170976974456</v>
+        <v>0.2323600964913043</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.08688575319449254</v>
+        <v>0.08581308957480749</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2382206628627504</v>
+        <v>0.2401206628627504</v>
       </c>
       <c r="C83">
-        <v>-83.51562673378481</v>
+        <v>-85.22462213671402</v>
       </c>
       <c r="D83">
-        <v>30.57997217120304</v>
+        <v>30.28097181648356</v>
       </c>
       <c r="E83">
-        <v>113.2100940840152</v>
+        <v>114.6200891322249</v>
       </c>
       <c r="F83">
-        <v>114.2095989049879</v>
+        <v>115.6195939531976</v>
       </c>
       <c r="G83">
         <v>0.114</v>
@@ -8075,37 +8075,37 @@
         <v>2.311</v>
       </c>
       <c r="M83">
-        <v>26.93062342179614</v>
+        <v>27.26310025416399</v>
       </c>
       <c r="N83">
-        <v>-24.61962342179614</v>
+        <v>-24.95210025416399</v>
       </c>
       <c r="O83">
-        <v>-4.185335981705344</v>
+        <v>-4.241857043207879</v>
       </c>
       <c r="P83">
-        <v>-20.4342874400908</v>
+        <v>-20.71024321095611</v>
       </c>
       <c r="Q83">
-        <v>-20.3992874400908</v>
+        <v>-20.67524321095611</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2632051826568101</v>
+        <v>0.2752832483599663</v>
       </c>
       <c r="T83">
-        <v>5.020904911242726</v>
+        <v>5.299844072978435</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01458822522771727</v>
+        <v>0.0144103200420134</v>
       </c>
       <c r="W83">
-        <v>0.2323600964913043</v>
+        <v>0.2324020465340933</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.08581308957480749</v>
+        <v>0.08476658848243179</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2401206628627504</v>
+        <v>0.2420206628627504</v>
       </c>
       <c r="C84">
-        <v>-85.22462213671402</v>
+        <v>-86.92782711303187</v>
       </c>
       <c r="D84">
-        <v>30.28097181648356</v>
+        <v>29.98776188837543</v>
       </c>
       <c r="E84">
-        <v>114.6200891322249</v>
+        <v>116.0300841804347</v>
       </c>
       <c r="F84">
-        <v>115.6195939531976</v>
+        <v>117.0295890014073</v>
       </c>
       <c r="G84">
         <v>0.114</v>
@@ -8157,37 +8157,37 @@
         <v>2.311</v>
       </c>
       <c r="M84">
-        <v>27.26310025416399</v>
+        <v>27.59557708653184</v>
       </c>
       <c r="N84">
-        <v>-24.95210025416399</v>
+        <v>-25.28457708653184</v>
       </c>
       <c r="O84">
-        <v>-4.241857043207879</v>
+        <v>-4.298378104710414</v>
       </c>
       <c r="P84">
-        <v>-20.71024321095611</v>
+        <v>-20.98619898182143</v>
       </c>
       <c r="Q84">
-        <v>-20.67524321095611</v>
+        <v>-20.95119898182143</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2752832483599663</v>
+        <v>0.288782262969376</v>
       </c>
       <c r="T84">
-        <v>5.299844072978435</v>
+        <v>5.611599606683049</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0144103200420134</v>
+        <v>0.0142367017282542</v>
       </c>
       <c r="W84">
-        <v>0.2324020465340933</v>
+        <v>0.2324429857324777</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.08476658848243179</v>
+        <v>0.0837453042838483</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2420206628627504</v>
+        <v>0.2439206628627504</v>
       </c>
       <c r="C85">
-        <v>-86.92782711303187</v>
+        <v>-88.62540825531492</v>
       </c>
       <c r="D85">
-        <v>29.98776188837543</v>
+        <v>29.70017579430212</v>
       </c>
       <c r="E85">
-        <v>116.0300841804347</v>
+        <v>117.4400792286444</v>
       </c>
       <c r="F85">
-        <v>117.0295890014073</v>
+        <v>118.439584049617</v>
       </c>
       <c r="G85">
         <v>0.114</v>
@@ -8239,37 +8239,37 @@
         <v>2.311</v>
       </c>
       <c r="M85">
-        <v>27.59557708653184</v>
+        <v>27.9280539188997</v>
       </c>
       <c r="N85">
-        <v>-25.28457708653184</v>
+        <v>-25.6170539188997</v>
       </c>
       <c r="O85">
-        <v>-4.298378104710414</v>
+        <v>-4.35489916621295</v>
       </c>
       <c r="P85">
-        <v>-20.98619898182143</v>
+        <v>-21.26215475268675</v>
       </c>
       <c r="Q85">
-        <v>-20.95119898182143</v>
+        <v>-21.22715475268675</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.288782262969376</v>
+        <v>0.3039686544049621</v>
       </c>
       <c r="T85">
-        <v>5.611599606683049</v>
+        <v>5.96232458210074</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0142367017282542</v>
+        <v>0.01406721718387022</v>
       </c>
       <c r="W85">
-        <v>0.2324429857324777</v>
+        <v>0.2324829501880434</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.0837453042838483</v>
+        <v>0.08274833637570722</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2439206628627504</v>
+        <v>0.2458206628627504</v>
       </c>
       <c r="C86">
-        <v>-88.62540825531489</v>
+        <v>-90.31752582627566</v>
       </c>
       <c r="D86">
-        <v>29.70017579430213</v>
+        <v>29.41805327155109</v>
       </c>
       <c r="E86">
-        <v>117.4400792286444</v>
+        <v>118.8500742768541</v>
       </c>
       <c r="F86">
-        <v>118.439584049617</v>
+        <v>119.8495790978267</v>
       </c>
       <c r="G86">
         <v>0.114</v>
@@ -8321,37 +8321,37 @@
         <v>2.311</v>
       </c>
       <c r="M86">
-        <v>27.9280539188997</v>
+        <v>28.26053075126755</v>
       </c>
       <c r="N86">
-        <v>-25.6170539188997</v>
+        <v>-25.94953075126755</v>
       </c>
       <c r="O86">
-        <v>-4.354899166212949</v>
+        <v>-4.411420227715483</v>
       </c>
       <c r="P86">
-        <v>-21.26215475268675</v>
+        <v>-21.53811052355206</v>
       </c>
       <c r="Q86">
-        <v>-21.22715475268675</v>
+        <v>-21.50311052355206</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3039686544049619</v>
+        <v>0.3211798980319594</v>
       </c>
       <c r="T86">
-        <v>5.962324582100736</v>
+        <v>6.359812887574119</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01406721718387023</v>
+        <v>0.01390172051111881</v>
       </c>
       <c r="W86">
-        <v>0.2324829501880434</v>
+        <v>0.2325219743034782</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.08274833637570722</v>
+        <v>0.08177482653599299</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2458206628627504</v>
+        <v>0.2477206628627504</v>
       </c>
       <c r="C87">
-        <v>-90.31752582627566</v>
+        <v>-92.00433405657135</v>
       </c>
       <c r="D87">
-        <v>29.41805327155109</v>
+        <v>29.14124008946512</v>
       </c>
       <c r="E87">
-        <v>118.8500742768541</v>
+        <v>120.2600693250638</v>
       </c>
       <c r="F87">
-        <v>119.8495790978267</v>
+        <v>121.2595741460365</v>
       </c>
       <c r="G87">
         <v>0.114</v>
@@ -8403,37 +8403,37 @@
         <v>2.311</v>
       </c>
       <c r="M87">
-        <v>28.26053075126755</v>
+        <v>28.5930075836354</v>
       </c>
       <c r="N87">
-        <v>-25.94953075126755</v>
+        <v>-26.2820075836354</v>
       </c>
       <c r="O87">
-        <v>-4.411420227715483</v>
+        <v>-4.467941289218018</v>
       </c>
       <c r="P87">
-        <v>-21.53811052355206</v>
+        <v>-21.81406629441738</v>
       </c>
       <c r="Q87">
-        <v>-21.50311052355206</v>
+        <v>-21.77906629441738</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3211798980319594</v>
+        <v>0.3408498907485279</v>
       </c>
       <c r="T87">
-        <v>6.359812887574119</v>
+        <v>6.814085236686556</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01390172051111881</v>
+        <v>0.01374007259819883</v>
       </c>
       <c r="W87">
-        <v>0.2325219743034782</v>
+        <v>0.2325600908813447</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.08177482653599299</v>
+        <v>0.08082395645999307</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2477206628627504</v>
+        <v>0.2496206628627504</v>
       </c>
       <c r="C88">
-        <v>-92.00433405657135</v>
+        <v>-93.68598142595555</v>
       </c>
       <c r="D88">
-        <v>29.14124008946512</v>
+        <v>28.86958776829066</v>
       </c>
       <c r="E88">
-        <v>120.2600693250638</v>
+        <v>121.6700643732736</v>
       </c>
       <c r="F88">
-        <v>121.2595741460365</v>
+        <v>122.6695691942462</v>
       </c>
       <c r="G88">
         <v>0.114</v>
@@ -8485,37 +8485,37 @@
         <v>2.311</v>
       </c>
       <c r="M88">
-        <v>28.5930075836354</v>
+        <v>28.92548441600326</v>
       </c>
       <c r="N88">
-        <v>-26.2820075836354</v>
+        <v>-26.61448441600326</v>
       </c>
       <c r="O88">
-        <v>-4.467941289218018</v>
+        <v>-4.524462350720554</v>
       </c>
       <c r="P88">
-        <v>-21.81406629441738</v>
+        <v>-22.0900220652827</v>
       </c>
       <c r="Q88">
-        <v>-21.77906629441738</v>
+        <v>-22.0550220652827</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3408498907485279</v>
+        <v>0.3635460361907223</v>
       </c>
       <c r="T88">
-        <v>6.814085236686556</v>
+        <v>7.338245639508599</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01374007259819883</v>
+        <v>0.01358214072925401</v>
       </c>
       <c r="W88">
-        <v>0.2325600908813447</v>
+        <v>0.2325973312160419</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.08082395645999307</v>
+        <v>0.07989494546620002</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2496206628627504</v>
+        <v>0.2515206628627504</v>
       </c>
       <c r="C89">
-        <v>-93.68598142595555</v>
+        <v>-95.36261092884983</v>
       </c>
       <c r="D89">
-        <v>28.86958776829066</v>
+        <v>28.6029533136061</v>
       </c>
       <c r="E89">
-        <v>121.6700643732736</v>
+        <v>123.0800594214833</v>
       </c>
       <c r="F89">
-        <v>122.6695691942462</v>
+        <v>124.0795642424559</v>
       </c>
       <c r="G89">
         <v>0.114</v>
@@ -8567,37 +8567,37 @@
         <v>2.311</v>
       </c>
       <c r="M89">
-        <v>28.92548441600326</v>
+        <v>29.25796124837111</v>
       </c>
       <c r="N89">
-        <v>-26.61448441600326</v>
+        <v>-26.94696124837111</v>
       </c>
       <c r="O89">
-        <v>-4.524462350720554</v>
+        <v>-4.580983412223089</v>
       </c>
       <c r="P89">
-        <v>-22.0900220652827</v>
+        <v>-22.36597783614802</v>
       </c>
       <c r="Q89">
-        <v>-22.0550220652827</v>
+        <v>-22.33097783614802</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3635460361907223</v>
+        <v>0.3900248725399492</v>
       </c>
       <c r="T89">
-        <v>7.338245639508599</v>
+        <v>7.949766109467649</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01358214072925401</v>
+        <v>0.01342779822096703</v>
       </c>
       <c r="W89">
-        <v>0.2325973312160419</v>
+        <v>0.232633725179496</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.07989494546620002</v>
+        <v>0.07898704835862957</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2515206628627504</v>
+        <v>0.2534206628627504</v>
       </c>
       <c r="C90">
-        <v>-95.36261092884983</v>
+        <v>-97.03436032533354</v>
       </c>
       <c r="D90">
-        <v>28.6029533136061</v>
+        <v>28.34119896533212</v>
       </c>
       <c r="E90">
-        <v>123.0800594214833</v>
+        <v>124.490054469693</v>
       </c>
       <c r="F90">
-        <v>124.0795642424559</v>
+        <v>125.4895592906657</v>
       </c>
       <c r="G90">
         <v>0.114</v>
@@ -8649,37 +8649,37 @@
         <v>2.311</v>
       </c>
       <c r="M90">
-        <v>29.25796124837111</v>
+        <v>29.59043808073896</v>
       </c>
       <c r="N90">
-        <v>-26.94696124837111</v>
+        <v>-27.27943808073896</v>
       </c>
       <c r="O90">
-        <v>-4.580983412223089</v>
+        <v>-4.637504473725624</v>
       </c>
       <c r="P90">
-        <v>-22.36597783614802</v>
+        <v>-22.64193360701334</v>
       </c>
       <c r="Q90">
-        <v>-22.33097783614802</v>
+        <v>-22.60693360701334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3900248725399492</v>
+        <v>0.4213180427708538</v>
       </c>
       <c r="T90">
-        <v>7.949766109467649</v>
+        <v>8.672472119419256</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01342779822096703</v>
+        <v>0.0132769240836528</v>
       </c>
       <c r="W90">
-        <v>0.232633725179496</v>
+        <v>0.2326693013010747</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.07898704835862957</v>
+        <v>0.0780995534332517</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2534206628627504</v>
+        <v>0.2553206628627503</v>
       </c>
       <c r="C91">
-        <v>-97.03436032533354</v>
+        <v>-98.7013623784772</v>
       </c>
       <c r="D91">
-        <v>28.34119896533212</v>
+        <v>28.08419196039818</v>
       </c>
       <c r="E91">
-        <v>124.490054469693</v>
+        <v>125.9000495179028</v>
       </c>
       <c r="F91">
-        <v>125.4895592906657</v>
+        <v>126.8995543388754</v>
       </c>
       <c r="G91">
         <v>0.114</v>
@@ -8731,37 +8731,37 @@
         <v>2.311</v>
       </c>
       <c r="M91">
-        <v>29.59043808073896</v>
+        <v>29.92291491310682</v>
       </c>
       <c r="N91">
-        <v>-27.27943808073896</v>
+        <v>-27.61191491310682</v>
       </c>
       <c r="O91">
-        <v>-4.637504473725624</v>
+        <v>-4.694025535228159</v>
       </c>
       <c r="P91">
-        <v>-22.64193360701334</v>
+        <v>-22.91788937787866</v>
       </c>
       <c r="Q91">
-        <v>-22.60693360701334</v>
+        <v>-22.88288937787866</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4213180427708538</v>
+        <v>0.4588698470479392</v>
       </c>
       <c r="T91">
-        <v>8.672472119419256</v>
+        <v>9.53971933136118</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0132769240836528</v>
+        <v>0.01312940270494554</v>
       </c>
       <c r="W91">
-        <v>0.2326693013010747</v>
+        <v>0.2327040868421738</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.0780995534332517</v>
+        <v>0.07723178061732672</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2553206628627503</v>
+        <v>0.2572206628627504</v>
       </c>
       <c r="C92">
-        <v>-98.7013623784772</v>
+        <v>-100.3637450788787</v>
       </c>
       <c r="D92">
-        <v>28.08419196039818</v>
+        <v>27.8318043082064</v>
       </c>
       <c r="E92">
-        <v>125.9000495179028</v>
+        <v>127.3100445661125</v>
       </c>
       <c r="F92">
-        <v>126.8995543388754</v>
+        <v>128.3095493870851</v>
       </c>
       <c r="G92">
         <v>0.114</v>
@@ -8813,37 +8813,37 @@
         <v>2.311</v>
       </c>
       <c r="M92">
-        <v>29.92291491310682</v>
+        <v>30.25539174547467</v>
       </c>
       <c r="N92">
-        <v>-27.61191491310682</v>
+        <v>-27.94439174547467</v>
       </c>
       <c r="O92">
-        <v>-4.694025535228159</v>
+        <v>-4.750546596730694</v>
       </c>
       <c r="P92">
-        <v>-22.91788937787866</v>
+        <v>-23.19384514874397</v>
       </c>
       <c r="Q92">
-        <v>-22.88288937787866</v>
+        <v>-23.15884514874397</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4588698470479392</v>
+        <v>0.5047664967199325</v>
       </c>
       <c r="T92">
-        <v>9.53971933136118</v>
+        <v>10.59968814595687</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01312940270494554</v>
+        <v>0.01298512355434175</v>
       </c>
       <c r="W92">
-        <v>0.2327040868421738</v>
+        <v>0.2327381078658862</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.07723178061732672</v>
+        <v>0.076383079731422</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2572206628627504</v>
+        <v>0.2591206628627504</v>
       </c>
       <c r="C93">
-        <v>-100.3637450788787</v>
+        <v>-102.0216318572</v>
       </c>
       <c r="D93">
-        <v>27.8318043082064</v>
+        <v>27.58391257809485</v>
       </c>
       <c r="E93">
-        <v>127.3100445661125</v>
+        <v>128.7200396143222</v>
       </c>
       <c r="F93">
-        <v>128.3095493870851</v>
+        <v>129.7195444352948</v>
       </c>
       <c r="G93">
         <v>0.114</v>
@@ -8895,37 +8895,37 @@
         <v>2.311</v>
       </c>
       <c r="M93">
-        <v>30.25539174547467</v>
+        <v>30.58786857784252</v>
       </c>
       <c r="N93">
-        <v>-27.94439174547467</v>
+        <v>-28.27686857784252</v>
       </c>
       <c r="O93">
-        <v>-4.750546596730694</v>
+        <v>-4.80706765823323</v>
       </c>
       <c r="P93">
-        <v>-23.19384514874397</v>
+        <v>-23.46980091960929</v>
       </c>
       <c r="Q93">
-        <v>-23.15884514874397</v>
+        <v>-23.43480091960929</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5047664967199325</v>
+        <v>0.5621373088099241</v>
       </c>
       <c r="T93">
-        <v>10.59968814595687</v>
+        <v>11.92464916420148</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01298512355434175</v>
+        <v>0.01284398090701194</v>
       </c>
       <c r="W93">
-        <v>0.2327381078658862</v>
+        <v>0.2327713893021266</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.076383079731422</v>
+        <v>0.0755528288647761</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2591206628627504</v>
+        <v>0.2610206628627504</v>
       </c>
       <c r="C94">
-        <v>-102.0216318572</v>
+        <v>-103.6751417854461</v>
       </c>
       <c r="D94">
-        <v>27.58391257809485</v>
+        <v>27.34039769805844</v>
       </c>
       <c r="E94">
-        <v>128.7200396143222</v>
+        <v>130.1300346625319</v>
       </c>
       <c r="F94">
-        <v>129.7195444352948</v>
+        <v>131.1295394835046</v>
       </c>
       <c r="G94">
         <v>0.114</v>
@@ -8977,37 +8977,37 @@
         <v>2.311</v>
       </c>
       <c r="M94">
-        <v>30.58786857784252</v>
+        <v>30.92034541021038</v>
       </c>
       <c r="N94">
-        <v>-28.27686857784252</v>
+        <v>-28.60934541021038</v>
       </c>
       <c r="O94">
-        <v>-4.80706765823323</v>
+        <v>-4.863588719735765</v>
       </c>
       <c r="P94">
-        <v>-23.46980091960929</v>
+        <v>-23.74575669047461</v>
       </c>
       <c r="Q94">
-        <v>-23.43480091960929</v>
+        <v>-23.71075669047461</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5621373088099241</v>
+        <v>0.6358997814970562</v>
       </c>
       <c r="T94">
-        <v>11.92464916420148</v>
+        <v>13.62817047337312</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01284398090701194</v>
+        <v>0.01270587358543117</v>
       </c>
       <c r="W94">
-        <v>0.2327713893021266</v>
+        <v>0.2328039550085553</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.0755528288647761</v>
+        <v>0.07474043285547749</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2610206628627504</v>
+        <v>0.2629206628627503</v>
       </c>
       <c r="C95">
-        <v>-103.6751417854461</v>
+        <v>-105.324389767676</v>
       </c>
       <c r="D95">
-        <v>27.34039769805844</v>
+        <v>27.10114476403829</v>
       </c>
       <c r="E95">
-        <v>130.1300346625319</v>
+        <v>131.5400297107417</v>
       </c>
       <c r="F95">
-        <v>131.1295394835046</v>
+        <v>132.5395345317143</v>
       </c>
       <c r="G95">
         <v>0.114</v>
@@ -9059,37 +9059,37 @@
         <v>2.311</v>
       </c>
       <c r="M95">
-        <v>30.92034541021038</v>
+        <v>31.25282224257824</v>
       </c>
       <c r="N95">
-        <v>-28.60934541021038</v>
+        <v>-28.94182224257824</v>
       </c>
       <c r="O95">
-        <v>-4.863588719735765</v>
+        <v>-4.920109781238301</v>
       </c>
       <c r="P95">
-        <v>-23.74575669047461</v>
+        <v>-24.02171246133994</v>
       </c>
       <c r="Q95">
-        <v>-23.71075669047461</v>
+        <v>-23.98671246133994</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6358997814970562</v>
+        <v>0.734249745079899</v>
       </c>
       <c r="T95">
-        <v>13.62817047337312</v>
+        <v>15.89953221893531</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01270587358543117</v>
+        <v>0.01257070471750105</v>
       </c>
       <c r="W95">
-        <v>0.2328039550085553</v>
+        <v>0.2328358278276133</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.07474043285547749</v>
+        <v>0.07394532186765324</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2629206628627503</v>
+        <v>0.2648206628627504</v>
       </c>
       <c r="C96">
-        <v>-105.324389767676</v>
+        <v>-106.9694867207865</v>
       </c>
       <c r="D96">
-        <v>27.10114476403829</v>
+        <v>26.86604285913747</v>
       </c>
       <c r="E96">
-        <v>131.5400297107417</v>
+        <v>132.9500247589514</v>
       </c>
       <c r="F96">
-        <v>132.5395345317143</v>
+        <v>133.949529579924</v>
       </c>
       <c r="G96">
         <v>0.114</v>
@@ -9141,37 +9141,37 @@
         <v>2.311</v>
       </c>
       <c r="M96">
-        <v>31.25282224257824</v>
+        <v>31.58529907494609</v>
       </c>
       <c r="N96">
-        <v>-28.94182224257824</v>
+        <v>-29.27429907494609</v>
       </c>
       <c r="O96">
-        <v>-4.920109781238301</v>
+        <v>-4.976630842740835</v>
       </c>
       <c r="P96">
-        <v>-24.02171246133994</v>
+        <v>-24.29766823220525</v>
       </c>
       <c r="Q96">
-        <v>-23.98671246133994</v>
+        <v>-24.26266823220525</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.734249745079899</v>
+        <v>0.8719396940958793</v>
       </c>
       <c r="T96">
-        <v>15.89953221893531</v>
+        <v>19.07943866272239</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01257070471750105</v>
+        <v>0.01243838150994841</v>
       </c>
       <c r="W96">
-        <v>0.2328358278276133</v>
+        <v>0.2328670296399542</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.07394532186765324</v>
+        <v>0.07316695005852003</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2648206628627504</v>
+        <v>0.2667206628627504</v>
       </c>
       <c r="C97">
-        <v>-106.9694867207865</v>
+        <v>-108.6105397459682</v>
       </c>
       <c r="D97">
-        <v>26.86604285913747</v>
+        <v>26.63498488216556</v>
       </c>
       <c r="E97">
-        <v>132.9500247589514</v>
+        <v>134.3600198071611</v>
       </c>
       <c r="F97">
-        <v>133.949529579924</v>
+        <v>135.3595246281338</v>
       </c>
       <c r="G97">
         <v>0.114</v>
@@ -9223,37 +9223,37 @@
         <v>2.311</v>
       </c>
       <c r="M97">
-        <v>31.58529907494609</v>
+        <v>31.91777590731394</v>
       </c>
       <c r="N97">
-        <v>-29.27429907494609</v>
+        <v>-29.60677590731394</v>
       </c>
       <c r="O97">
-        <v>-4.976630842740835</v>
+        <v>-5.03315190424337</v>
       </c>
       <c r="P97">
-        <v>-24.29766823220525</v>
+        <v>-24.57362400307057</v>
       </c>
       <c r="Q97">
-        <v>-24.26266823220525</v>
+        <v>-24.53862400307057</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8719396940958793</v>
+        <v>1.07847461761985</v>
       </c>
       <c r="T97">
-        <v>19.07943866272239</v>
+        <v>23.84929832840299</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01243838150994841</v>
+        <v>0.01230881503588645</v>
       </c>
       <c r="W97">
-        <v>0.2328670296399542</v>
+        <v>0.232897581414538</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.07316695005852003</v>
+        <v>0.0724047943287438</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2667206628627504</v>
+        <v>0.2686206628627504</v>
       </c>
       <c r="C98">
-        <v>-108.6105397459682</v>
+        <v>-110.2476522913881</v>
       </c>
       <c r="D98">
-        <v>26.63498488216556</v>
+        <v>26.40786738495531</v>
       </c>
       <c r="E98">
-        <v>134.3600198071611</v>
+        <v>135.7700148553708</v>
       </c>
       <c r="F98">
-        <v>135.3595246281337</v>
+        <v>136.7695196763435</v>
       </c>
       <c r="G98">
         <v>0.114</v>
@@ -9305,37 +9305,37 @@
         <v>2.311</v>
       </c>
       <c r="M98">
-        <v>31.91777590731393</v>
+        <v>32.25025273968179</v>
       </c>
       <c r="N98">
-        <v>-29.60677590731393</v>
+        <v>-29.93925273968179</v>
       </c>
       <c r="O98">
-        <v>-5.033151904243369</v>
+        <v>-5.089672965745905</v>
       </c>
       <c r="P98">
-        <v>-24.57362400307057</v>
+        <v>-24.84957977393589</v>
       </c>
       <c r="Q98">
-        <v>-24.53862400307057</v>
+        <v>-24.81457977393589</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.078474617619847</v>
+        <v>1.422699490159796</v>
       </c>
       <c r="T98">
-        <v>23.84929832840293</v>
+        <v>31.79906443787057</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01230881503588645</v>
+        <v>0.01218192003551649</v>
       </c>
       <c r="W98">
-        <v>0.232897581414538</v>
+        <v>0.2329275032556252</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.0724047943287438</v>
+        <v>0.07165835315009694</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2686206628627504</v>
+        <v>0.2705206628627503</v>
       </c>
       <c r="C99">
-        <v>-110.2476522913881</v>
+        <v>-111.880924306621</v>
       </c>
       <c r="D99">
-        <v>26.40786738495531</v>
+        <v>26.18459041793223</v>
       </c>
       <c r="E99">
-        <v>135.7700148553708</v>
+        <v>137.1800099035806</v>
       </c>
       <c r="F99">
-        <v>136.7695196763435</v>
+        <v>138.1795147245532</v>
       </c>
       <c r="G99">
         <v>0.114</v>
@@ -9387,37 +9387,37 @@
         <v>2.311</v>
       </c>
       <c r="M99">
-        <v>32.25025273968179</v>
+        <v>32.58272957204964</v>
       </c>
       <c r="N99">
-        <v>-29.93925273968179</v>
+        <v>-30.27172957204964</v>
       </c>
       <c r="O99">
-        <v>-5.089672965745905</v>
+        <v>-5.146194027248439</v>
       </c>
       <c r="P99">
-        <v>-24.84957977393589</v>
+        <v>-25.1255355448012</v>
       </c>
       <c r="Q99">
-        <v>-24.81457977393589</v>
+        <v>-25.0905355448012</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.422699490159796</v>
+        <v>2.111149235239694</v>
       </c>
       <c r="T99">
-        <v>31.79906443787057</v>
+        <v>47.69859665680585</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01218192003551649</v>
+        <v>0.01205761472903162</v>
       </c>
       <c r="W99">
-        <v>0.2329275032556252</v>
+        <v>0.2329568144468943</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.07165835315009694</v>
+        <v>0.07092714546489187</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2705206628627503</v>
+        <v>0.2724206628627504</v>
       </c>
       <c r="C100">
-        <v>-111.880924306621</v>
+        <v>-113.5104523893104</v>
       </c>
       <c r="D100">
-        <v>26.18459041793223</v>
+        <v>25.96505738345248</v>
       </c>
       <c r="E100">
-        <v>137.1800099035806</v>
+        <v>138.5900049517903</v>
       </c>
       <c r="F100">
-        <v>138.1795147245532</v>
+        <v>139.5895097727629</v>
       </c>
       <c r="G100">
         <v>0.114</v>
@@ -9469,37 +9469,37 @@
         <v>2.311</v>
       </c>
       <c r="M100">
-        <v>32.58272957204964</v>
+        <v>32.9152064044175</v>
       </c>
       <c r="N100">
-        <v>-30.27172957204964</v>
+        <v>-30.6042064044175</v>
       </c>
       <c r="O100">
-        <v>-5.146194027248439</v>
+        <v>-5.202715088750975</v>
       </c>
       <c r="P100">
-        <v>-25.1255355448012</v>
+        <v>-25.40149131566652</v>
       </c>
       <c r="Q100">
-        <v>-25.0905355448012</v>
+        <v>-25.36649131566652</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.111149235239694</v>
+        <v>4.176498470479387</v>
       </c>
       <c r="T100">
-        <v>47.69859665680585</v>
+        <v>95.39719331361171</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01205761472903162</v>
+        <v>0.01193582064085959</v>
       </c>
       <c r="W100">
-        <v>0.2329568144468943</v>
+        <v>0.2329855334928853</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.07092714546489187</v>
+        <v>0.07021070965211518</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2724206628627504</v>
-      </c>
-      <c r="C101">
-        <v>-113.5104523893104</v>
-      </c>
-      <c r="D101">
-        <v>25.96505738345248</v>
-      </c>
-      <c r="E101">
-        <v>138.5900049517903</v>
-      </c>
-      <c r="F101">
-        <v>139.5895097727629</v>
-      </c>
-      <c r="G101">
-        <v>0.114</v>
-      </c>
-      <c r="H101">
-        <v>140</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.346</v>
-      </c>
-      <c r="K101">
-        <v>0.035</v>
-      </c>
-      <c r="L101">
-        <v>2.311</v>
-      </c>
-      <c r="M101">
-        <v>32.9152064044175</v>
-      </c>
-      <c r="N101">
-        <v>-30.6042064044175</v>
-      </c>
-      <c r="O101">
-        <v>-5.202715088750975</v>
-      </c>
-      <c r="P101">
-        <v>-25.40149131566652</v>
-      </c>
-      <c r="Q101">
-        <v>-25.36649131566652</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.176498470479387</v>
-      </c>
-      <c r="T101">
-        <v>95.39719331361171</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01193582064085959</v>
-      </c>
-      <c r="W101">
-        <v>0.2329855334928853</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.07021070965211518</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
